--- a/input/images/tables/us_core_reqs.xlsx
+++ b/input/images/tables/us_core_reqs.xlsx
@@ -418,7 +418,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>﻿Is_New</t>
+          <t>Is_New</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Servers may deploy and support one or more US Core Profiles to represent clinical information</t>
+          <t>Servers **MAY** deploy and support one or more US Core Profiles to represent clinical information</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>This has an AND logic with one OR more of 4-8.  Restated: Servers MAY support requirement 3 and any requirement 4-8</t>
+          <t>This has an AND logic with one OR more of 4-8.  Restated: Servers **MAY** support requirement 3 and any requirement 4-8</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -873,7 +873,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Server may deploy and support ... the following US Core interaction: “Quick Start” defined for each Profile</t>
+          <t>Server **MAY** deploy and support ... the following US Core interaction: “Quick Start” defined for each Profile</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Server may deploy and support ... the following US Core interaction: [Clinical Notes](https://hl7.org/fhir/us/core/clinical-notes.html)</t>
+          <t>Server **MAY** deploy and support ... the following US Core interaction: [Clinical Notes](https://hl7.org/fhir/us/core/clinical-notes.html)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Server may deploy and support ... the following US Core interaction: [Medication List](https://hl7.org/fhir/us/core/medication-list.html)</t>
+          <t>Server **MAY** deploy and support ... the following US Core interaction: [Medication List](https://hl7.org/fhir/us/core/medication-list.html)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Server may deploy and support ... the following US Core interaction: [Basic Provenance](https://hl7.org/fhir/us/core/basic-provenance.html)</t>
+          <t>Server **MAY** deploy and support ... the following US Core interaction: [Basic Provenance](https://hl7.org/fhir/us/core/basic-provenance.html)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Server may deploy and support ... the following US Core interaction: [Screening and Assessments](https://hl7.org/fhir/us/core/screening-and-assessments.html)</t>
+          <t>Server **MAY** deploy and support ... the following US Core interaction: [Screening and Assessments](https://hl7.org/fhir/us/core/screening-and-assessments.html)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>A Server that certifies to the [21st Century Cures Act for accessing patient data](https://www.federalregister.gov/d/2020-07419/p-1177) **SHALL** implement all components in the USCDI [[USCDI link](https://www.healthit.gov/isp/united-states-core-data-interoperability-uscdi)]</t>
+          <t>Certifying Systems **SHALL** implement all components in the USCDI [[USCDI link](https://www.healthit.gov/isp/united-states-core-data-interoperability-uscdi)]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>A Server that certifies to the [21st Century Cures Act for accessing patient data](https://www.federalregister.gov/d/2020-07419/p-1177) **SHALL** implement all components in the ... the US Core CapabilityStatement [[Definition](https://hl7.org/fhir/us/core/CapabilityStatement-us-core-Server.html)] .</t>
+          <t>Certifying Systems **SHALL** implement all components in the ... the US Core CapabilityStatement [[Definition](https://hl7.org/fhir/us/core/CapabilityStatement-us-core-Server.html)] .</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Both 21 and 22 should be true</t>
+          <t>Both 21 and 22 **SHOULD**be true</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[When using an [extensible Binding] (http://hl7.org/fhir/R4/terminologies.html#extensible)] If no suitable code exists in the [extensible] ValueSet, alternate code(s) **MAY** be used..</t>
+          <t>[When using an [extensible Binding] (http://hl7.org/fhir/R4/terminologies.html#extensible)] If no suitable code exists in the [extensible] ValueSet, alternate code(s) **MAY**  be used..</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alternate codes may be provided in addition to the standard codes defined in required or extensible ValueSets. These alternate codes are called "additional codings".</t>
+          <t>Alternate codes **MAY** be provided in addition to the standard codes defined in required or extensible ValueSets. These alternate codes are called "additional codings".</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[The additional codings] may be equivalent to or narrower in meaning than the standard concept code.</t>
+          <t>[The additional codings] **MAY** be equivalent to or narrower in meaning than the standard concept code.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Servers **MAY** communicate a system-wide profile in their CapabilityStatement to identify which additional elements, including modifier elements, they support</t>
+          <t>Servers **MAY**  communicate a system-wide profile in their CapabilityStatement to identify which additional elements, including modifier elements, they support</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>**MAY** to may</t>
+          <t>**MAY**  to may</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>receivers SHOULD accept instances that ... contain unexpected data elements  [[definition](http://hl7.org/fhir/R4/conformance-rules.html#isModifier)]</t>
+          <t>receivers **SHOULD** accept instances that ... contain unexpected data elements  [[definition](http://hl7.org/fhir/R4/conformance-rules.html#isModifier)]</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>receivers SHOULD [NOT] accept instances that ... contain unexpected data elements … when those elements are modifier elements [[definition](http://hl7.org/fhir/R4/conformance-rules.html#isModifier)]</t>
+          <t>receivers **SHOULD NOT** accept instances that ... contain unexpected data elements … when those elements are modifier elements [[definition](http://hl7.org/fhir/R4/conformance-rules.html#isModifier)]</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>This test should be conducted if requirement 42 is true. If the source system does not have data for a Mandatory element, the following must occur.</t>
+          <t>This test **SHOULD**be conducted if requirement 42 is true. If the source system does not have data for a Mandatory element, the following must occur.</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>When searching using the `token` type searchparameter [(how to search by token)](http://hl7.org/fhir/R4/search.html#token) The Client … **MAY** provide both the system and code values.</t>
+          <t>When searching using the `token` type searchparameter [(how to search by token)](http://hl7.org/fhir/R4/search.html#token) The Client … **MAY**  provide both the system and code values.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>When searching using the `reference` type searchparameter [(how to search by reference)](http://hl7.org/fhir/R4/search.html#reference) The Client … **MAY** provide both the Type and id values.</t>
+          <t>When searching using the `reference` type searchparameter [(how to search by reference)](http://hl7.org/fhir/R4/search.html#reference) The Client … **MAY**  provide both the Type and id values.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Servers are strongly encouraged to support a query for resources without requiring a status parameter.</t>
+          <t>Servers **SHOULD** support a query for resources without requiring a status parameter.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>For searches where the Client does not supply a status parameter, an implementation’s business rules may override the FHIR RESTful search expectations and require a status parameter to be provided</t>
+          <t>For searches where the Client does not supply a status parameter, an implementation’s business rules **MAY** override the FHIR RESTful search expectations and require a status parameter to be provided</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -7079,15 +7079,15 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>is expected to **SHALL**</t>
+          <t>duplicate of base cardinality rules</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>If any sub-element is marked as Must Support [for a complex element], it must also meet the Must Support requirements and satisfy the Must Support requirements for the parent element.</t>
+          <t>If any sub-element is marked as Must Support [for a complex element], it **SHALL** also meet the Must Support requirements and satisfy the Must Support requirements for the parent element.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>[I]f any sub-element is marked as Must Support [for a complex element] and the parent element is not… [and] the parent element is represented in the structure, Servers **SHALL** support the sub-element(s) marked as Must Support.</t>
+          <t>[I]f any sub-element is marked as Must Support [for a complex element] and the parent element is not… [and] the parent element is present in an instance, Servers **SHALL** support the sub-element(s) marked as Must Support.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -9696,20 +9696,20 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>The U.S. Core Data for Interoperability (USCDI) may require additional elements, [which is a requirement for certification in the ONC IT Health Certification program, but not a requirement of US Core conformance for US Core Responders]</t>
+          <t>The U.S. Core Data for Interoperability (USCDI) **MAY** require additional elements, [which is a requirement for certification in the ONC IT Health Certification program, but not a requirement of US Core conformance for US Core Responders]</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Remove "The [U.S. Core Data for Interoperability (USCDI)] may require additional elements such as `Patient.suffix` Add somewhere else a note that USCDI may update its requirements retroactively…</t>
+          <t>Remove "The [U.S. Core Data for Interoperability (USCDI)] **MAY** require additional elements such as `Patient.suffix`</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -9785,18 +9785,22 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>The U.S. Core Data for Interoperability (USCDI) may require additional elements, [which is a requirement for certification in the ONC IT Health Certification program, but not a requirement of US Core conformance for US Core Requestors]</t>
+          <t>The U.S. Core Data for Interoperability (USCDI) **MAY** require additional elements, [which is a requirement for certification in the ONC IT Health Certification program, but not a requirement of US Core conformance for US Core Requestors]</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>5</v>
-      </c>
-      <c r="I105" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Remove "The [U.S. Core Data for Interoperability (USCDI)] **MAY** require additional elements such as `Patient.suffix`</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>Client</t>
@@ -9870,7 +9874,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>In certain profiles, only specific resource references are labeled as Must Support.
+          <t>When a Reference type element is labeled as *Must Support*, has multiple target profiles referenced, and specific targets are labeled as *Must Support*,"
 ...
 - US Core Responders **SHALL** be capable of providing [such an element] with a valid reference to [all listed Must Support profile(s).]</t>
         </is>
@@ -9969,9 +9973,9 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>In certain profiles, only specific resource references are labeled as Must Support.
+          <t>When a Reference type element is labeled as *Must Support*, has multiple target profiles referenced, and specific targets are labeled as *Must Support*,"
 ...
-- US Core Requestors **SHALL** be capable of processing [such an element] with a valid reference to [all listed Must Support profile(s).]</t>
+- US Core Responders **SHALL** be capable of providing [such an element] with a valid reference to [all listed Must Support profile(s).]</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -10218,7 +10222,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>In specific profiles, only a single resource reference is present on an element labeled Must Support.
+          <t>When a Reference type element is labeled as *Must Support* and has a single target profile referenced
 ...
 - US Core Responders **SHALL** be capable of providing [such an element] with a valid reference to [the Must Support Profile.]</t>
         </is>
@@ -10317,9 +10321,9 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>In specific profiles, only a single resource reference is present on an element labeled Must Support.
-…
-- US Core Requestors **SHALL** be capable of processing [such an element] with a valid reference to [the Must Support Profile.]</t>
+          <t>When a Reference type element is labeled as *Must Support* and has a single target profile referenced
+...
+- US Core Responders **SHALL** be capable of providing [such an element] with a valid reference to [the Must Support Profile.]</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -10614,7 +10618,7 @@
         <is>
           <t>[If a profile has] a Must Support element [with] a choice of datatypes for its content [and some of] the datatypes … are labeled as Must Support[, or a profile has] an Additional USCDI element [with] a choice of datatypes for its content [and some of] the datatypes … are labeled as Additional USCDI
 …
-[US Core Requestors] **MAY** support ... processing other [data type] choice elements (such as Observation.effectivePeriod), but this is not a requirement of US Core.</t>
+[US Core Requestors] **MAY**  support ... processing other [data type] choice elements (such as Observation.effectivePeriod), but this is not a requirement of US Core.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10627,7 +10631,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>**MAY** to can</t>
+          <t>**MAY**  to can</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -10716,7 +10720,7 @@
         <is>
           <t>[If a profile has] a Must Support element [with] a choice of datatypes for its content [and some of] the datatypes … are labeled as Must Support[, or a profile has] an Additional USCDI element [with] a choice of datatypes for its content [and some of] the datatypes … are labeled as Additional USCDI
 …
-[US Core Responders] **MAY** support populating ... other [data type] choice elements (such as Observation.effectivePeriod), but this is not a requirement of US Core.</t>
+[US Core Responders] **MAY**  support populating ... other [data type] choice elements (such as Observation.effectivePeriod), but this is not a requirement of US Core.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10729,7 +10733,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>**MAY** to can</t>
+          <t>**MAY**  to can</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -11008,7 +11012,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>An individual SMART Server will publish a granular list of its capabilities, and a set of these capabilities is combined to support a specific use, a Capability Set. See SMART App Launch’s [FHIR OAuth authorization Endpoints and Capabilities](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#smart-on-fhir-oauth-authorization-endpoints-and-capabilities) for more details. Servers **MAY** support ... [any] SMART on FHIR Capability Sets and capabilities [(see [FHIR OAuth authorization Endpoints and Capabilities](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#smart-on-fhir-oauth-authorization-endpoints-and-capabilities))]</t>
+          <t>An individual SMART Server will publish a granular list of its capabilities, and a set of these capabilities is combined to support a specific use, a Capability Set. See SMART App Launch’s [FHIR OAuth authorization Endpoints and Capabilities](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#smart-on-fhir-oauth-authorization-endpoints-and-capabilities) for more details. Servers **MAY**  support ... [any] SMART on FHIR Capability Sets and capabilities [(see [FHIR OAuth authorization Endpoints and Capabilities](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#smart-on-fhir-oauth-authorization-endpoints-and-capabilities))]</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -11021,7 +11025,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>**MAY** to may?</t>
+          <t>**MAY**  to may?</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -11129,7 +11133,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Either Patient access or clinician access should be supported when support User facing applications</t>
+          <t>Either Patient access or clinician access **SHOULD**be supported when support User facing applications</t>
         </is>
       </c>
       <c r="O119" t="inlineStr"/>
@@ -11224,7 +11228,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Both patient access and clinician shall be supported, when participating in ONC certification program</t>
+          <t>Both patient access and clinician **SHALL** be supported, when participating in ONC certification program</t>
         </is>
       </c>
       <c r="O120" t="inlineStr"/>
@@ -11659,7 +11663,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Implementations meeting US EHR certification [of the ONC IT Health Certification program] requirements must support all US Core’s required scopes.</t>
+          <t>Certifying systems **SHALL** support all US Core’s required scopes.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -11748,7 +11752,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Other systems only need to support scopes for the US Core APIs they support [instead of all US Core's required scopes]</t>
+          <t>Other systems **MAY**  support scopes for the US Core APIs they support [instead of all US Core's required scopes]</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11761,7 +11765,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>change "need" to "**MAY**?</t>
+          <t>change "need" to "**MAY** ?</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -11829,7 +11833,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Servers **MAY** support other scopes in addition to those listed below and in the Quick Start sections.</t>
+          <t>Servers **MAY**  support other scopes in addition to those listed below and in the Quick Start sections.</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -11914,7 +11918,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>US Core Clients should follow the [principle of least privilege](https://en.wikipedia.org/wiki/Principle_of_least_privilege) and access only the necessary resources.</t>
+          <t>US Core Clients **SHOULD**follow the [principle of least privilege](https://en.wikipedia.org/wiki/Principle_of_least_privilege) and access only the necessary resources.</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -14645,7 +14649,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>The following scopes that correspond directly to FHIR resource types **MAY** be supported
+          <t>The following scopes that correspond directly to FHIR resource types **MAY**  be supported
 ...
 [For] Location [the] &lt;patient|user|system&gt;/Location.rs [see [SMART Clinical Scope Syntax](https://hl7.org/fhir/smart-app-launch/STU2/scopes-and-launch-context.html#clinical-scope-syntax) for details on clinical data scopes]</t>
         </is>
@@ -14704,7 +14708,7 @@
       <c r="AB157" t="inlineStr"/>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Change in v8.0.0: "The Following Resource Level Scopes MAY Be Supported" -&gt; "The following scopes that correspond directly to FHIR resource types **MAY** be supported"</t>
+          <t>Change in v8.0.0: "The Following Resource Level Scopes **MAY** Be Supported" -&gt; "The following scopes that correspond directly to FHIR resource types **MAY**  be supported"</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr"/>
@@ -14732,7 +14736,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>The following scopes that correspond directly to FHIR resource types **MAY** be supported
+          <t>The following scopes that correspond directly to FHIR resource types **MAY**  be supported
 ...
 [For] Medication [the] &lt;patient|user|system&gt;/Medication.rs [see [SMART Clinical Scope Syntax](https://hl7.org/fhir/smart-app-launch/STU2/scopes-and-launch-context.html#clinical-scope-syntax) for details on clinical data scopes]</t>
         </is>
@@ -14791,7 +14795,7 @@
       <c r="AB158" t="inlineStr"/>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Change in v8.0.0: "The Following Resource Level Scopes MAY Be Supported" -&gt; "The following scopes that correspond directly to FHIR resource types **MAY** be supported"</t>
+          <t>Change in v8.0.0: "The Following Resource Level Scopes **MAY** Be Supported" -&gt; "The following scopes that correspond directly to FHIR resource types **MAY**  be supported"</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr"/>
@@ -15739,7 +15743,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>US Core requires ... additional metadata [to be available through the Server's [Well-Known Uniform Resource Identifier (URI)](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#using-well-known)]: ... [in] `scopes_supported` [the] array of scopes a Client may request.... The Server **SHALL** list all the required US Core Scopes for the US Core Profiles they support in the scopes_supported array</t>
+          <t>US Core requires ... additional metadata [to be available through the Server's [Well-Known Uniform Resource Identifier (URI)](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#using-well-known)]: ... [in] `scopes_supported` [the] array of scopes a Client **MAY** request.... The Server **SHALL** list all the required US Core Scopes for the US Core Profiles they support in the scopes_supported array</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -15836,7 +15840,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>US Core requires ... additional metadata [to be available through the Server's [Well-Known Uniform Resource Identifier (URI)](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#using-well-known)]: ... [in] `scopes_supported` [the] array of scopes a Client may request. The Server [MAY support] additional scopes (so Clients should not consider … [the required scopes] an exhaustive list).</t>
+          <t>US Core requires ... additional metadata [to be available through the Server's [Well-Known Uniform Resource Identifier (URI)](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#using-well-known)]: ... [in] `scopes_supported` [the] array of scopes a Client **MAY** request. The Server [MAY support] additional scopes (so Clients **SHOULD**not consider … [the required scopes] an exhaustive list).</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -15921,7 +15925,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>US Core requires ... additional metadata [to be available through the Server's [Well-Known Uniform Resource Identifier (URI)](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#using-well-known)]: ... [in] `scopes_supported` [the] array of scopes a Client may request. Servers **MAY**  limit Clients’ scopes to those configured at registration time.</t>
+          <t>US Core requires ... additional metadata [to be available through the Server's [Well-Known Uniform Resource Identifier (URI)](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#using-well-known)]: ... [in] `scopes_supported` [the] array of scopes a Client **MAY** request. Servers **MAY**   limit Clients’ scopes to those configured at registration time.</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -16006,7 +16010,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>US Core requires ... additional metadata [to be available through the Server's [Well-Known Uniform Resource Identifier (URI)](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#using-well-known)]: ... [in] `scopes_supported` [the] array of scopes a Client may request. … Servers **SHALL** allow users to select a subset of the requested scopes at the approval time.</t>
+          <t>US Core requires ... additional metadata [to be available through the Server's [Well-Known Uniform Resource Identifier (URI)](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#using-well-known)]: ... [in] `scopes_supported` [the] array of scopes a Client **MAY** request. … Servers **SHALL** allow users to select a subset of the requested scopes at the approval time.</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -16095,7 +16099,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>US Core requires ... additional metadata [to be available through the Server's [Well-Known Uniform Resource Identifier (URI)](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#using-well-known)]: ... [in] `scopes_supported` [the] array of scopes a Client may request. The app **SHOULD** inspect the returned scopes and accommodate the differences from the scopes it asked for and registered.</t>
+          <t>US Core requires ... additional metadata [to be available through the Server's [Well-Known Uniform Resource Identifier (URI)](https://hl7.org/fhir/smart-app-launch/STU2/conformance.html#using-well-known)]: ... [in] `scopes_supported` [the] array of scopes a Client **MAY** request. The app **SHOULD** inspect the returned scopes and accommodate the differences from the scopes it asked for and registered.</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -16860,7 +16864,7 @@
       <c r="AB181" t="inlineStr"/>
       <c r="AC181" t="inlineStr">
         <is>
-          <t xml:space="preserve">It could be argued that this is a shall, but putting this requirement as a should in keeping with similar conformance designations of the other general guidance requirements. </t>
+          <t xml:space="preserve">It could be argued that this is a **SHALL**, but putting this requirement as a **SHOULD**in keeping with similar conformance designations of the other general guidance requirements. </t>
         </is>
       </c>
       <c r="AD181" t="inlineStr"/>
@@ -16888,7 +16892,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>[When using SNOMED codes in US Core Profiles I]mplementers **MAY**  use the default system URI [of [SNOMED CT](http://snomed.info/sct)], which refers to an unspecified edition/version [of SNOMED]</t>
+          <t>[When using SNOMED codes in US Core Profiles I]mplementers **MAY**   use the default system URI [of [SNOMED CT](http://snomed.info/sct)], which refers to an unspecified edition/version [of SNOMED]</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -17066,7 +17070,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>[If a] US Core Profiles binds the Quantity.code element in the Quantity datatype to the [UCUM](http://unitsofmeasure.org/) code system, [then] systems should also use UCUM for the optional valueRange and valueRatio datatypes (which are complex datatypes with Quantity elements)</t>
+          <t>[If a] US Core Profiles binds the Quantity.code element in the Quantity datatype to the [UCUM](http://unitsofmeasure.org/) code system, [then] systems **SHOULD**also use UCUM for the optional valueRange and valueRatio datatypes (which are complex datatypes with Quantity elements)</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -17224,7 +17228,7 @@
       <c r="AB185" t="inlineStr"/>
       <c r="AC185" t="inlineStr">
         <is>
-          <t xml:space="preserve">It could be argued that this is a shall, but putting this requirement as a should in keeping with similar conformance designations of the other general guidance requirements. </t>
+          <t xml:space="preserve">It could be argued that this is a **SHALL**, but putting this requirement as a **SHOULD**in keeping with similar conformance designations of the other general guidance requirements. </t>
         </is>
       </c>
       <c r="AD185" t="inlineStr"/>
@@ -17313,7 +17317,7 @@
       <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="inlineStr">
         <is>
-          <t xml:space="preserve">It could be argued that this is a shall, but putting this requirement as a should in keeping with similar conformance designations of the other general guidance requirements. </t>
+          <t xml:space="preserve">It could be argued that this is a **SHALL**, but putting this requirement as a **SHOULD**in keeping with similar conformance designations of the other general guidance requirements. </t>
         </is>
       </c>
       <c r="AD186" t="inlineStr"/>
@@ -17406,7 +17410,7 @@
       <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="inlineStr">
         <is>
-          <t xml:space="preserve">It could be argued that this is a shall, but putting this requirement as a should in keeping with similar conformance designations of the other general guidance requirements. </t>
+          <t xml:space="preserve">It could be argued that this is a **SHALL**, but putting this requirement as a **SHOULD**in keeping with similar conformance designations of the other general guidance requirements. </t>
         </is>
       </c>
       <c r="AD187" t="inlineStr"/>
@@ -17894,7 +17898,7 @@
         <is>
           <t>If the FHIR Server has updated the resource status to entered-in-error:
 ...
-For provider-facing applications, the content may be supplied with content and additional detail (such as the reason for the status change) that the patient viewing system would typically not have access to.</t>
+For provider-facing applications, the content **MAY** be supplied with content and additional detail (such as the reason for the status change) that the patient viewing system would typically not have access to.</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -18072,7 +18076,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>[When Clients request a resource in a specific language] Clients **MAY**  request language/locale using the http [Accept-Language](https://www.ietf.org/rfc/rfc2616.txt) header.</t>
+          <t>[When Clients request a resource in a specific language] Clients **MAY**   request language/locale using the http [Accept-Language](https://www.ietf.org/rfc/rfc2616.txt) header.</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -18085,7 +18089,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>MAY to **MAY**</t>
+          <t xml:space="preserve">MAY to **MAY** </t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -20641,7 +20645,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Systems [Servers] may extend their capabilities [around types of clinical notes] to the complete US Core DocumentReference Type Value Set.</t>
+          <t>Systems [Servers] **MAY** extend their capabilities [around types of clinical notes] to the complete US Core DocumentReference Type Value Set.</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -20654,7 +20658,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>may to **MAY**</t>
+          <t xml:space="preserve">may to **MAY** </t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -20734,7 +20738,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>This guide requires [Server] systems to implement the [US Core DocumentReference Profile](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html)</t>
+          <t>Systems  **SHALL** implement the [US Core DocumentReference Profile](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html)</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -20827,7 +20831,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>This guide requires [Server] systems to implement the [US Core DiagnosticReport Profile for Report and Note exchange](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-diagnosticreport-note.html)</t>
+          <t>Systems **SHALL**  implement the [US Core DiagnosticReport Profile for Report and Note exchange](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-diagnosticreport-note.html)</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -20920,7 +20924,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Systems [Servers] may support other [DiagnosticReport] categories as well.</t>
+          <t>Systems [Servers] **MAY** support other [DiagnosticReport] categories as well.</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -20933,7 +20937,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>may to **MAY**</t>
+          <t xml:space="preserve">may to **MAY** </t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -21013,7 +21017,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Systems [Clients] may support other [DiagnosticReport] categories as well.</t>
+          <t>Systems [Clients] **MAY** support other [DiagnosticReport] categories as well.</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -21026,7 +21030,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>may to **MAY**</t>
+          <t xml:space="preserve">may to **MAY** </t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -21425,7 +21429,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Servers that support DiagnosticReport will include the clinical note narrative content in  `DiagnosticReport.presentedForm`</t>
+          <t>Servers that support DiagnosticReport **SHALL**  include the clinical note narrative content in  `DiagnosticReport.presentedForm`</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -21518,7 +21522,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>a Client can determine the note and report types supported by a Server by invoking the standard FHIR Value Set Expansion ([$expand](http://hl7.org/fhir/R4/valueset-operation-expand.html)) operation defined in the FHIR R4 specification.</t>
+          <t>a Client **MAY**  determine the note and report types supported by a Server by invoking the standard FHIR Value Set Expansion ([$expand](http://hl7.org/fhir/R4/valueset-operation-expand.html)) operation defined in the FHIR R4 specification.</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -21531,7 +21535,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>can to **MAY**</t>
+          <t xml:space="preserve">can to **MAY** </t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -22761,15 +22765,15 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H247" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>are permitted  to can or **MAY**</t>
+          <t>remove as self evident</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -22920,17 +22924,20 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/medication-list.html#options-for-representing-medication</t>
+          <t xml:space="preserve">https://hl7.org/fhir/us/core/STU8/medication-list.html#options-for-representing-medication, https://build.fhir.org/ig/HL7/US-Core/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, 
+https://build.fhir.org/ig/HL7/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, https://build.fhir.org/ig/HL7/US-Core/StructureDefinition-us-core-medication.html#profile-specific-implementation-guidance
+</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>medication-list.html#options-for-representing-medication</t>
+          <t xml:space="preserve">medication-list.html#options-for-representing-medication, StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medication.html#profile-specific-implementation-guidance
+</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>USCDI recommends the [National Drug Codes (NDC)](https://www.fda.gov/drugs/drug-approvals-and-databases/national-drug-code-directory) as an optional medication terminology. They can be supplied as an additional coding element [when representing a medication]</t>
+          <t>USCDI recommends the [National Drug Codes (NDC)](https://www.fda.gov/drugs/drug-approvals-and-databases/national-drug-code-directory) as an optional medication terminology. They **MAY**  be supplied as an additional coding element [when representing a medication]</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -22961,17 +22968,19 @@
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr">
         <is>
-          <t>medication-list</t>
+          <t>medication-list,StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest,StructureDefinition-us-core-medication</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>options-for-representing-medication</t>
+          <t xml:space="preserve">options-for-representing-medication,profile-specific-implementation-guidance,profile-specific-implementation-guidance,profile-specific-implementation-guidance
+</t>
         </is>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>Medication-List: Options-For-Representing-Medication</t>
+          <t xml:space="preserve">Medication-List: Options-For-Representing-Medication, Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medication: Profile-Specific-Implementation-Guidance
+</t>
         </is>
       </c>
       <c r="V249" t="inlineStr"/>
@@ -23011,7 +23020,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>When referencing the Medication resource, the resource may be included in the returned bundle, as an external resource, or as a [contained](http://hl7.org/fhir/R4/references.html#contained) resource if it can’t stand alone. … The Server application **MAY** choose any combination of these methods</t>
+          <t>When referencing the Medication resource, the resource **MAY** be included in the returned bundle, as an external resource, or as a [contained](http://hl7.org/fhir/R4/references.html#contained) resource if it can’t stand alone. … The Server application **MAY**  choose any combination of these methods</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -23037,7 +23046,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>Servers may any combination of support inline code, reference to medication resources, and reference to contained medication resource</t>
+          <t>Servers **MAY** any combination of support inline code, reference to medication resources, and reference to contained medication resource</t>
         </is>
       </c>
       <c r="O250" t="inlineStr"/>
@@ -23227,7 +23236,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>Clients shall support  support inline code, reference to medication resources, and reference to contained medication resource</t>
+          <t>Clients **SHALL** support  support inline code, reference to medication resources, and reference to contained medication resource</t>
         </is>
       </c>
       <c r="O252" t="inlineStr"/>
@@ -23778,15 +23787,15 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H258" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>may to **MAY**</t>
+          <t>not a conf</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -24246,7 +24255,7 @@
       <c r="F263" t="inlineStr">
         <is>
           <t>Requirements to access “all medications” [all historical, active, and future prescribed medications and medications entered in error and whose status is unknown.] and “all active medications” [all medications with an active status. Active medications do not include past, future, unknown status, and entered-in-error medications.] for a patient:
-Servers **MAY** support the search parameters `category`and `encounter`. This search will return all medications ordered during an encounter for a given MedicationRequest.category such as "inpatient".</t>
+Servers **MAY**  support the search parameters `category`and `encounter`. This search will return all medications ordered during an encounter for a given MedicationRequest.category such as "inpatient".</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -24312,9 +24321,9 @@
       <c r="AC263" t="inlineStr">
         <is>
           <t>Change in v8.0.0:
-The category and encounter elements MAY be used together to get the intersection of medications for a given encounter (i.e., the context) that were administered during as an inpatient (i.e., the category).
+The category and encounter elements **MAY** be used together to get the intersection of medications for a given encounter (i.e., the context) that were administered during as an inpatient (i.e., the category).
 -&gt;
-Servers MAY support the search parameters category and encounter. This search will return all medications ordered during an encounter for a given MedicationRequest.category such as "inpatient".</t>
+Servers **MAY** support the search parameters category and encounter. This search will return all medications ordered during an encounter for a given MedicationRequest.category such as "inpatient".</t>
         </is>
       </c>
       <c r="AD263" t="inlineStr"/>
@@ -24342,7 +24351,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>To provide a list of a patient’s medications, it may be necessary to “de-duplicate” them. The de-duplication activity **MAY** be  supplied by the Server</t>
+          <t>To provide a list of a patient’s medications, it **MAY** be necessary to “de-duplicate” them. The de-duplication activity **MAY**  be  supplied by the Server</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -24431,7 +24440,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>To provide a list of a patient’s medications, it may be necessary to “de-duplicate” them. The de-duplication activity ... **SHOULD** be provided by the Client.</t>
+          <t>To provide a list of a patient’s medications, it **MAY** be necessary to “de-duplicate” them. The de-duplication activity ... **SHOULD** be provided by the Client.</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -24520,7 +24529,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Transformation of data from one format to another **MAY** change the authorship of the information, where the HIE is the author/author organization</t>
+          <t>Transformation of data from one format to another **MAY**  change the authorship of the information, where the HIE is the author/author organization</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -24533,7 +24542,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>**MAY** to can</t>
+          <t>**MAY**  to can</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -24585,7 +24594,7 @@
       <c r="AB266" t="inlineStr"/>
       <c r="AC266" t="inlineStr">
         <is>
-          <t>This is less a US Core requirement and more guidance on how data intermediaries should act, so marked as DEPRECATED</t>
+          <t>This is less a US Core requirement and more guidance on how data intermediaries **SHOULD**act, so marked as DEPRECATED</t>
         </is>
       </c>
       <c r="AD266" t="inlineStr"/>
@@ -24702,7 +24711,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>An agent.type=”assembler”, agent.type=”transmitter”, or other agents from [Provenance Agent Type](https://hl7.org/fhir/us/core/STU8/ValueSet-us-core-provenance-participant-type.html) value set **MAY** also be included.</t>
+          <t>An agent.type=”assembler”, agent.type=”transmitter”, or other agents from [Provenance Agent Type](https://hl7.org/fhir/us/core/STU8/ValueSet-us-core-provenance-participant-type.html) value set **MAY**  also be included.</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -25163,7 +25172,7 @@
       <c r="F273" t="inlineStr">
         <is>
           <t>For API developers using US Core, it’s important to understand when to use the QuestionnaireResponse versus Observation to represent structured assessments and surveys. Here are some guidelines to help choose the appropriate profile:
-Observations represent specific point-in-time facts that need to be searched, trended, the subject of statistical analysis, and directly referenced in support of other actions ... anything that meets one of the preceding criteria must be surfaced as an Observation.</t>
+Observations represent specific point-in-time facts that need to be searched, trended, the subject of statistical analysis, and directly referenced in support of other actions ... anything that meets one of the preceding criteria **SHOULD** be surfaced as an Observation.</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -25224,7 +25233,7 @@
       <c r="AB273" t="inlineStr"/>
       <c r="AC273" t="inlineStr">
         <is>
-          <t>Included because it specifically references how developers should build things to function correctly.</t>
+          <t>Included because it specifically references how developers **SHOULD**build things to function correctly.</t>
         </is>
       </c>
       <c r="AD273" t="inlineStr">
@@ -25344,7 +25353,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>For FHIR implementers, it is important to note that QuestionnaireResponse [which represent the source-of-truth of a completed form, shall] references a specific version of a form, whether it was represented as a FHIR Questionnaire or not. This reference provides the context of exactly what options were available, what logic was used to calculate answers, and what questions were asked.</t>
+          <t>For FHIR implementers, it is important to note that QuestionnaireResponse [which represent the source-of-truth of a completed form, **SHALL**] references a specific version of a form, whether it was represented as a FHIR Questionnaire or not. This reference provides the context of exactly what options were available, what logic was used to calculate answers, and what questions were asked.</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -25435,7 +25444,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>API consumers can query by category  when accessing patient information.</t>
+          <t>API consumers **MAY**  query by category  when accessing patient information.</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -25448,7 +25457,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>can to **MAY**</t>
+          <t xml:space="preserve">can to **MAY** </t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -26046,7 +26055,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>A Server may support Version DSTU2 and Argonaut Data Query</t>
+          <t>A Server **MAY** support Version DSTU2 and Argonaut Data Query</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -26059,7 +26068,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>"A Server may support Version DSTU2 and Argonaut Data Query or FHIR R4 and US Core ver 3.1.1+ or both.  A Server may make explicit ...". To  "In practice, a server may support Argonaut Data Query in FHIR DSTU2, and one or more versions of US Core in FHIR R4. Sometimes, the Server explicitly names the version of Argo/US Core on its FHIR endpoint (e.g., a "DSTU2" or "R4" path component, or separate files based on version)."</t>
+          <t>"A Server **MAY** support Version DSTU2 and Argonaut Data Query or FHIR R4 and US Core ver 3.1.1+ or both.  A Server **MAY** make explicit ...". To  "In practice, a server **MAY** support Argonaut Data Query in FHIR DSTU2, and one or more versions of US Core in FHIR R4. Sometimes, the Server explicitly names the version of Argo/US Core on its FHIR endpoint (e.g., a "DSTU2" or "R4" path component, or separate files based on version)."</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -26135,7 +26144,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>A Server may support … FHIR R4 and US Core ver 3.1.1+</t>
+          <t>A Server **MAY** support … FHIR R4 and US Core ver 3.1.1+</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -26148,7 +26157,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>"A Server may support Version DSTU2 and Argonaut Data Query or FHIR R4 and US Core ver 3.1.1+ or both.  A Server may make explicit ...". To  "In practice, a server may support Argonaut Data Query in FHIR DSTU2, and one or more versions of US Core in FHIR R4. Sometimes, the Server explicitly names the version of Argo/US Core on its FHIR endpoint (e.g., a "DSTU2" or "R4" path component, or separate files based on version)."</t>
+          <t>"A Server **MAY** support Version DSTU2 and Argonaut Data Query or FHIR R4 and US Core ver 3.1.1+ or both.  A Server **MAY** make explicit ...". To  "In practice, a server **MAY** support Argonaut Data Query in FHIR DSTU2, and one or more versions of US Core in FHIR R4. Sometimes, the Server explicitly names the version of Argo/US Core on its FHIR endpoint (e.g., a "DSTU2" or "R4" path component, or separate files based on version)."</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -26224,7 +26233,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>A Server may support [both] [(]Version DSTU2 and Argonaut Data Query[) and (] FHIR R4 and US Core ver 3.1.1+[)]</t>
+          <t>A Server **MAY** support [both] [(]Version DSTU2 and Argonaut Data Query[) and (] FHIR R4 and US Core ver 3.1.1+[)]</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -26237,7 +26246,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>"A Server may support Version DSTU2 and Argonaut Data Query or FHIR R4 and US Core ver 3.1.1+ or both.  A Server may make explicit ...". To  "In practice, a server may support Argonaut Data Query in FHIR DSTU2, and one or more versions of US Core in FHIR R4. Sometimes, the Server explicitly names the version of Argo/US Core on its FHIR endpoint (e.g., a "DSTU2" or "R4" path component, or separate files based on version)."</t>
+          <t>"A Server **MAY** support Version DSTU2 and Argonaut Data Query or FHIR R4 and US Core ver 3.1.1+ or both.  A Server **MAY** make explicit ...". To  "In practice, a server **MAY** support Argonaut Data Query in FHIR DSTU2, and one or more versions of US Core in FHIR R4. Sometimes, the Server explicitly names the version of Argo/US Core on its FHIR endpoint (e.g., a "DSTU2" or "R4" path component, or separate files based on version)."</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -26313,7 +26322,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>A Server may make explicit which version of Argo/US Core is on their FHIR endpoint (e.g., “DSTU2” or “R4” path component or separate files based on version).</t>
+          <t>A Server **MAY** make explicit which version of Argo/US Core is on their FHIR endpoint (e.g., “DSTU2” or “R4” path component or separate files based on version).</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -26326,7 +26335,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>"A Server may support Version DSTU2 and Argonaut Data Query or FHIR R4 and US Core ver 3.1.1+ or both.  A Server may make explicit ...". To  "In practice, a server may support Argonaut Data Query in FHIR DSTU2, and one or more versions of US Core in FHIR R4. Sometimes, the Server explicitly names the version of Argo/US Core on its FHIR endpoint (e.g., a "DSTU2" or "R4" path component, or separate files based on version)."</t>
+          <t>"A Server **MAY** support Version DSTU2 and Argonaut Data Query or FHIR R4 and US Core ver 3.1.1+ or both.  A Server **MAY** make explicit ...". To  "In practice, a server **MAY** support Argonaut Data Query in FHIR DSTU2, and one or more versions of US Core in FHIR R4. Sometimes, the Server explicitly names the version of Argo/US Core on its FHIR endpoint (e.g., a "DSTU2" or "R4" path component, or separate files based on version)."</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -26739,7 +26748,7 @@
       <c r="F291" t="inlineStr">
         <is>
           <t>The FHIR RESTful resource types supported in a DSTU2 implementation **SHOULD** be supported in a R4 implementation [with the] exception [of]
-MedicationStatement may be deprecated, and the data **SHOULD** be mapped to MedicationRequest.</t>
+MedicationStatement **MAY** be deprecated, and the data **SHOULD** be mapped to MedicationRequest.</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -26992,7 +27001,7 @@
       <c r="F294" t="inlineStr">
         <is>
           <t>The FHIR RESTful resource types supported in a DSTU2 implementation **SHOULD** be supported in a R4 implementation [with the] exception [of]
-MedicationStatement may be deprecated, and the data **SHOULD** be mapped to MedicationRequest.</t>
+MedicationStatement **MAY** be deprecated, and the data **SHOULD** be mapped to MedicationRequest.</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -28031,8 +28040,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Profile Specific Implementation Guidance:
-No Known Allergies may be represented using the US Core-AllergyIntolerance profile</t>
+          <t>No Known Allergies **MAY** be represented using the US Core-AllergyIntolerance profile</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -28045,7 +28053,7 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>may to **MAY**</t>
+          <t xml:space="preserve">may to **MAY** </t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
@@ -28125,7 +28133,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>[When used No Known Allergies is documented the system **SHALL** use an] appropriate negation code in AllergyIntolerence.code</t>
+          <t>[When No Known Allergies is documented the system **SHALL** use an] appropriate negation code in AllergyIntolerance.code</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -28214,7 +28222,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>[When used No Known Allergies is documented the system **SHALL** use an] verification status in AllergyIntolerance.verificationStatus</t>
+          <t>[When No Known Allergies is documented the system **SHALL** use an] verification status in AllergyIntolerance.verificationStatus</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -28305,7 +28313,7 @@
         <is>
           <t>If a patient has not been asked about their allergies, this would be represented as:
 AllergyIntolerance.code = “1631000175102” (Patient not asked (contextual qualifier) (qualifier value))
-AllergyIntolerance.verificationStatus = “unconfirmed” or empty (in other words, then element omitted)</t>
+AllergyIntolerance.verificationStatus = “unconfirmed” or empty (in other words, the element omitted)</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -28639,7 +28647,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Considerations for systems aligning with [HL7 Consolidated (C-CDA)] (http://www.hl7.org/implement/standards/product_brief.cfm?product_id=492) Care Plan requirements: Assessment and Plan **MAY** be  included as narrative in CarePlan.text</t>
+          <t>Considerations for systems aligning with [HL7 Consolidated (C-CDA)] (http://www.hl7.org/implement/standards/product_brief.cfm?product_id=492) Care Plan requirements: Assessment and Plan **MAY**  be  included as narrative in CarePlan.text</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -29332,15 +29340,15 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>SHOULD</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H321" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>none to **SHOULD**</t>
+          <t>deprecated is guidance USCDI data element cover this one.</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
@@ -29509,7 +29517,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>[Historical Encounter Diagnosis records **MAY**  have a] Condition.code … [from the] base “preferred” … [value set] binding.</t>
+          <t>[Historical Encounter Diagnosis records **MAY**   have a] Condition.code … [from the] base “preferred” … [value set] binding.</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -30221,15 +30229,15 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>SHOULD</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H331" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>none to **SHOULD**</t>
+          <t>deprecated is guidance USCDI data element cover this one.</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
@@ -30331,7 +30339,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>If condition.category has a category of problem-list-item, then condition.clinicalStatus should be present</t>
+          <t>If condition.category has a category of problem-list-item, then condition.clinicalStatus **SHOULD**be present</t>
         </is>
       </c>
       <c r="O332" t="inlineStr"/>
@@ -30484,7 +30492,7 @@
       <c r="F334" t="inlineStr">
         <is>
           <t>Updates to .meta.lastUpdated **SHOULD** reflect:
-Changes in the clinical status or verifications status of problems or health concerns.</t>
+Changes in the clinical status or verification status of problems or health concerns.</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -30570,7 +30578,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>A coverage.type of “81” (Self-pay) **MAY** be  used to imply that the patient has no coverage or that an individual or organization other than an insurer is taking responsibility for payment for a portion of the health care costs.</t>
+          <t>A coverage.type of “81” (Self-pay) **MAY**  be  used to imply that the patient has no coverage or that an individual or organization other than an insurer is taking responsibility for payment for a portion of the health care costs.</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -30651,20 +30659,20 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Implementers should refer to the [PHDSC Payer Type Committee User’s Guide](https://www.nahdo.org/sites/default/files/2020-12/SourceofPaymentTypologyUsersGuideVersion9.2December2020.pdf) for the Source of Payment Typology when selecting codes.</t>
+          <t>Implementers **SHOULD**refer to the [PHDSC Payer Type Committee User’s Guide](https://www.nahdo.org/sites/default/files/2020-12/SourceofPaymentTypologyUsersGuideVersion9.2December2020.pdf) for the Source of Payment Typology when selecting codes.</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>SHOULD</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">can to **SHOULD** ? </t>
+          <t>sentence remove in 9 Ballot FHIR-44122</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
@@ -30736,7 +30744,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>To differentiate Medicare Parts A, B, C, and D systems can use the following codes [when sending Coverage.type]: [For] Part A and B [use] 121 (Medicare Fee For Service)</t>
+          <t>To differentiate Medicare Parts A, B, C, and D systems **SHOULD** use the following codes [when sending Coverage.type]: [For] Part A and B [use] 121 (Medicare Fee For Service)</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -30817,7 +30825,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>To differentiate Medicare Parts A, B, C, and D systems can use the following codes: [For] Part C (Medicare Advantage Plan) [use] 111 (Medicare HMO), 112 (Medicare PPO), 113 (Medicare POS)</t>
+          <t>To differentiate Medicare Parts A, B, C, and D systems **SHOULD** use the following codes: [For] Part C (Medicare Advantage Plan) [use] 111 (Medicare HMO), 112 (Medicare PPO), 113 (Medicare POS)</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -30898,7 +30906,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>To differentiate Medicare Parts A, B, C, and D systems can use the following codes: [For] Part D [use] 122 (Medicare Drug Benefit)</t>
+          <t>To differentiate Medicare Parts A, B, C, and D systems **SHOULD** use the following codes: [For] Part D [use] 122 (Medicare Drug Benefit)</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -30979,7 +30987,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>If Insurers issue unique member IDs for dependents, then the memberId Coverage.identifier should be used [with the unique dependent ID] instead of Coverage.dependent to uniquely refer to the dependent with respect to their insurance.</t>
+          <t>If Insurers issue unique member IDs for dependents, then the memberId Coverage.identifier **SHOULD**be used [with the unique dependent ID] instead of Coverage.dependent to uniquely refer to the dependent with respect to their insurance.</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -31145,7 +31153,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Implementers are encouraged to use the FDA Global UDI Database (GUDID) and associated APIs to parse and validate the [unique device ID] UDI</t>
+          <t>Implementers **SHOULD** use the FDA Global UDI Database (GUDID) and associated APIs to parse and validate the [unique device ID] UDI</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -31566,7 +31574,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Servers SHOULD support query by Device.type to allow Clients to request the patient’s devices by a specific type.</t>
+          <t>Servers **SHOULD** support query by Device.type to allow Clients to request the patient’s devices by a specific type.</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -31651,7 +31659,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Records of implanted devices **MAY** be  queried against UDI data, including: UDI HRF string (udi-carrier)</t>
+          <t>Records of implanted devices **MAY**  be  queried against UDI data, including: UDI HRF string (udi-carrier)</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -31732,7 +31740,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Records of implanted devices **MAY** be  queried against UDI data, including:UDI Device Identifier (udi-di)</t>
+          <t>Records of implanted devices **MAY**  be  queried against UDI data, including:UDI Device Identifier (udi-di)</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -31813,7 +31821,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Records of implanted devices **MAY** be  queried against UDI data, including: Manufacturer (manufacturer)</t>
+          <t>Records of implanted devices **MAY**  be  queried against UDI data, including: Manufacturer (manufacturer)</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -31894,7 +31902,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Records of implanted devices **MAY** be  queried against UDI data, including: Model number (model)</t>
+          <t>Records of implanted devices **MAY**  be  queried against UDI data, including: Model number (model)</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -31975,7 +31983,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Implementers **MAY** also adopt custom SearchParameters for searching by lot numbers</t>
+          <t>Implementers **MAY**  also adopt custom SearchParameters for searching by lot numbers</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -32056,7 +32064,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Implementers **MAY** also adopt custom SearchParameters for searching by serial number</t>
+          <t>Implementers **MAY**  also adopt custom SearchParameters for searching by serial number</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -32137,7 +32145,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Implementers **MAY** also adopt custom SearchParameters for searching by expiration date</t>
+          <t>Implementers **MAY**  also adopt custom SearchParameters for searching by expiration date</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -32218,7 +32226,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Implementers **MAY** also adopt custom SearchParameters for searching by manufacture date</t>
+          <t>Implementers **MAY**  also adopt custom SearchParameters for searching by manufacture date</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -32299,7 +32307,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Implementers **MAY** also adopt custom SearchParameters for searching by distinct identifier</t>
+          <t>Implementers **MAY**  also adopt custom SearchParameters for searching by distinct identifier</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -32735,15 +32743,15 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H361" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>"Must  Support, at a Minimum " to **SHALL**</t>
+          <t>duplicates minimum binding</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
@@ -32815,7 +32823,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Other [diagnostic report] categories may be supported [when using US Core DiagnosticReport Profile for Report and Note Exchange]</t>
+          <t>Other [diagnostic report] categories **MAY** be supported [when using US Core DiagnosticReport Profile for Report and Note Exchange]</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -32828,7 +32836,7 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>may to **MAY**</t>
+          <t xml:space="preserve">may to **MAY** </t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
@@ -32900,20 +32908,20 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>[L]inkages between specific LOINC codes and the LP-type codes may be used as guidance [for a Server's categorization of diagnostic reports]</t>
+          <t>[L]inkages between specific LOINC codes and the LP-type codes **MAY** be used as guidance [for a Server's categorization of diagnostic reports]</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H363" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>may to **MAY**</t>
+          <t>not a conf</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -33074,7 +33082,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>For Diagnostic Imaging Reports systems **SHOULD** support using the subset of LOINC codes listed Table 4: LOINC® Document Type Codes in *HL7 Standard for CDA® Release 2: Imaging Integration; Basic Imaging Reports in CDA and DICOM, Release 1*</t>
+          <t>For Diagnostic Imaging Reports systems **SHOULD** support using the subset of LOINC codes listed in Table 4: LOINC® Document Type Codes in *HL7 Standard for CDA® Release 2: Imaging Integration; Basic Imaging Reports in CDA and DICOM, Release 1*</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -33168,15 +33176,15 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H366" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>Must Support, at a minimum to **SHALL**</t>
+          <t>duplicates minimum binding</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -33221,9 +33229,9 @@
       <c r="AC366" t="inlineStr">
         <is>
           <t>Change in v8.0.0: 
-The DocumentReference.type binding Must Support, at a minimum, the 5 Common Clinical Notes and may extend to the whole US Core DocumentReference Type Value Set
+The DocumentReference.type binding Must Support, at a minimum, the 5 Common Clinical Notes and **MAY** extend to the whole US Core DocumentReference Type Value Set
 -&gt;
-The DocumentReference.type binding Must Support, at a minimum, the 10 Common Clinical Notes and may extend to the whole US Core DocumentReference Type Value Set</t>
+The DocumentReference.type binding Must Support, at a minimum, the 10 Common Clinical Notes and **MAY** extend to the whole US Core DocumentReference Type Value Set</t>
         </is>
       </c>
       <c r="AD366" t="inlineStr">
@@ -33255,7 +33263,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>The DocumentReference.type binding may extend to the whole [US Core DocumentReference Type Value Set](https://hl7.org/fhir/us/core/STU8/ValueSet-us-core-documentreference-type.html)</t>
+          <t>The DocumentReference.type binding **MAY** extend to the whole [US Core DocumentReference Type Value Set](https://hl7.org/fhir/us/core/STU8/ValueSet-us-core-documentreference-type.html)</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -33336,7 +33344,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>[DocumentReference.type may also use] other category schemes such as the LOINC-based [Document Class Value Set](http://hl7.org/fhir/R4/valueset-document-classcodes.html) and [IHE XDSclassCode](https://wiki.ihe.net/index.php/XDS_classCode_Metadata_Coding_System)</t>
+          <t>[DocumentReference.type **MAY** also use] other category schemes such as the LOINC-based [Document Class Value Set](http://hl7.org/fhir/R4/valueset-document-classcodes.html) and [IHE XDSclassCode](https://wiki.ihe.net/index.php/XDS_classCode_Metadata_Coding_System)</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -33407,12 +33415,12 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, file:///Users/ehaas/Documents/FHIR/US-Core/output/StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -33443,7 +33451,7 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>Either DocumentReference.attachment.url or DocumentReference.attachment.data  shall be supported though both are marked must support</t>
+          <t>Either DocumentReference.attachment.url or DocumentReference.attachment.data  **SHALL** be supported though both are marked must support</t>
         </is>
       </c>
       <c r="O369" t="inlineStr"/>
@@ -33452,17 +33460,17 @@
       <c r="R369" t="inlineStr"/>
       <c r="S369" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference</t>
+          <t>StructureDefinition-us-core-documentreference,StructureDefinition-us-core-adi-documentreference</t>
         </is>
       </c>
       <c r="T369" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U369" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Adi-Documentreference: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V369" t="inlineStr">
@@ -33500,12 +33508,12 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, file:///Users/ehaas/Documents/FHIR/US-Core/output/StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -33541,17 +33549,17 @@
       <c r="R370" t="inlineStr"/>
       <c r="S370" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference</t>
+          <t>StructureDefinition-us-core-documentreference,StructureDefinition-us-core-adi-documentreference</t>
         </is>
       </c>
       <c r="T370" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U370" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Adi-Documentreference: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V370" t="inlineStr">
@@ -33585,12 +33593,12 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, file:///Users/ehaas/Documents/FHIR/US-Core/output/StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -33626,17 +33634,17 @@
       <c r="R371" t="inlineStr"/>
       <c r="S371" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference</t>
+          <t>StructureDefinition-us-core-documentreference,StructureDefinition-us-core-adi-documentreference</t>
         </is>
       </c>
       <c r="T371" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U371" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Adi-Documentreference: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V371" t="inlineStr">
@@ -33670,12 +33678,12 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, file:///Users/ehaas/Documents/FHIR/US-Core/output/StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -33711,17 +33719,17 @@
       <c r="R372" t="inlineStr"/>
       <c r="S372" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference</t>
+          <t>StructureDefinition-us-core-documentreference,StructureDefinition-us-core-adi-documentreference</t>
         </is>
       </c>
       <c r="T372" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U372" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Adi-Documentreference: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V372" t="inlineStr">
@@ -33755,12 +33763,12 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, file:///Users/ehaas/Documents/FHIR/US-Core/output/StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -33796,17 +33804,17 @@
       <c r="R373" t="inlineStr"/>
       <c r="S373" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference</t>
+          <t>StructureDefinition-us-core-documentreference,StructureDefinition-us-core-adi-documentreference</t>
         </is>
       </c>
       <c r="T373" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U373" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Adi-Documentreference: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V373" t="inlineStr">
@@ -33840,12 +33848,12 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, file:///Users/ehaas/Documents/FHIR/US-Core/output/StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -33881,17 +33889,17 @@
       <c r="R374" t="inlineStr"/>
       <c r="S374" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference</t>
+          <t>StructureDefinition-us-core-documentreference,StructureDefinition-us-core-adi-documentreference</t>
         </is>
       </c>
       <c r="T374" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U374" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Adi-Documentreference: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V374" t="inlineStr">
@@ -33925,12 +33933,12 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, file:///Users/ehaas/Documents/FHIR/US-Core/output/StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-documentreference.html#profile-specific-implementation-guidance, StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -33966,17 +33974,17 @@
       <c r="R375" t="inlineStr"/>
       <c r="S375" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference</t>
+          <t>StructureDefinition-us-core-documentreference,StructureDefinition-us-core-adi-documentreference</t>
         </is>
       </c>
       <c r="T375" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U375" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Adi-Documentreference: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V375" t="inlineStr">
@@ -34046,7 +34054,7 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servers shall support either Encounter.reasonCode or  Encounter.reasonReference </t>
+          <t xml:space="preserve">Servers **SHALL** support either Encounter.reasonCode or  Encounter.reasonReference </t>
         </is>
       </c>
       <c r="O376" t="inlineStr"/>
@@ -34313,7 +34321,7 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>If Encounter.reasonReference references an Observation then the observation should conform to a US Core observation profile</t>
+          <t>If Encounter.reasonReference references an Observation then the observation **SHOULD**conform to a US Core observation profile</t>
         </is>
       </c>
       <c r="O379" t="inlineStr"/>
@@ -34398,7 +34406,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t>Servers shall support either Encounter.location.location or Encounter.serviceProvider</t>
+          <t>Servers **SHALL** support either Encounter.location.location or Encounter.serviceProvider</t>
         </is>
       </c>
       <c r="O380" t="inlineStr"/>
@@ -34813,7 +34821,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>If the event facility/location differs from the Encounter.location … systems **MAY**  use the standard [Event Location Extension](http://hl7.org/fhir/StructureDefinition/event-location) for US Core DiagnosticReport Profile for Laboratory Results Reporting and US Core Observation Clinical Result Profile.</t>
+          <t>If the event facility/location differs from the Encounter.location … systems **MAY**   use the standard [Event Location Extension](http://hl7.org/fhir/StructureDefinition/event-location) for US Core DiagnosticReport Profile for Laboratory Results Reporting and US Core Observation Clinical Result Profile.</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -35329,7 +35337,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>[Servers shall] use the status code: not-done to represent that an immunization was not given.</t>
+          <t>Servers **SHALL** use the status code: not-done to represent that an immunization was not given.</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -35427,15 +35435,15 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H392" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>are required to **SHALL**  ( this requirement restates  the binding?)</t>
+          <t>this requirement restates  the binding</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
@@ -35613,15 +35621,15 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>SHOULD</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H394" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>"preferred"  to **SHOULD**</t>
+          <t>remove preferred is guidance</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
@@ -35694,13 +35702,17 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SHOULD</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H395" t="n">
-        <v>3</v>
-      </c>
-      <c r="I395" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>remove preferred is guidance</t>
+        </is>
+      </c>
       <c r="J395" t="inlineStr">
         <is>
           <t>Server</t>
@@ -35933,15 +35945,15 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H398" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>"are used" to **SHALL**  ( this requirement restates  the binding?)</t>
+          <t xml:space="preserve"> this requirement restates  the binding</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
@@ -36022,15 +36034,15 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H399" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>" recommends as optional " to **MAY**</t>
+          <t xml:space="preserve"> this requirement restates  the binding</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -36102,7 +36114,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>When referencing a Medication resource in .medicationReference, the resource may be [contained](http://hl7.org/fhir/R4/references.html#contained)</t>
+          <t>When referencing a Medication resource in .medicationReference, the resource **MAY** be [contained](http://hl7.org/fhir/R4/references.html#contained)</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -36183,7 +36195,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>When referencing a Medication resource in .medicationReference, the resource may be an external resource</t>
+          <t>When referencing a Medication resource in .medicationReference, the resource **MAY** be an external resource</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
@@ -36290,7 +36302,7 @@
       </c>
       <c r="N402" t="inlineStr">
         <is>
-          <t>Servers shall support either a medication code or a medication reference</t>
+          <t>Servers **SHALL** support either a medication code or a medication reference</t>
         </is>
       </c>
       <c r="O402" t="inlineStr"/>
@@ -36625,11 +36637,11 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H406" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -36730,11 +36742,11 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H407" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
@@ -37922,7 +37934,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>The observations **MAY**  have additional codes that translate or map to the Observation code or category codes [such as] … local system-specific codes [and] …more specific codes</t>
+          <t>The observations **MAY**   have additional codes that translate or map to the Observation code or category codes [such as] … local system-specific codes [and] …more specific codes</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
@@ -38521,7 +38533,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Systems that never provide a component observation without a component value … [MAY choose not] to support Observation.component.dataAbsentReason</t>
+          <t>Systems that never provide a component observation without a component value **MAY**  choose not to support Observation.component.dataAbsentReason</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -38534,7 +38546,7 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>"are not required to support" to **MAY**</t>
+          <t xml:space="preserve">"are not required to support" to **MAY** </t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -38699,7 +38711,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>[For] an Observation without a value … [Systems **MAY** choose not to] include a reason why the data is absent … [if] there are component observations or … reporting panel observations using Observation.hasMember</t>
+          <t>[For] an Observation without a value … [Systems **MAY**  choose not to] include a reason why the data is absent … [if] there are component observations or … reporting panel observations using Observation.hasMember</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
@@ -38712,7 +38724,7 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>"unless there are …" to **MAY**</t>
+          <t xml:space="preserve">"unless there are …" to **MAY** </t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
@@ -38729,7 +38741,7 @@
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t>When sending an Observation without a value systems are may choose not to send data absent reason if there are component observations or reporting panel observations using observation.hasMember</t>
+          <t>When sending an Observation without a value systems are **MAY** choose not to send data absent reason if there are component observations or reporting panel observations using observation.hasMember</t>
         </is>
       </c>
       <c r="O429" t="inlineStr"/>
@@ -38788,7 +38800,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Systems that never provide an observation without a value ... [MAY choose not] to support Observation.dataAbsentReason</t>
+          <t>Systems that never provide an observation without a value **MAY**  choose not to support Observation.dataAbsentReason</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -38801,7 +38813,7 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>"are not required to support" to **MAY**</t>
+          <t xml:space="preserve">"are not required to support" to **MAY** </t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
@@ -39047,7 +39059,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>[When sending US Core Observation Occupation Profile] for … [a] current job, [Servers SHALL] omit observation.effectivePeriod.end to indicate it is ongoing.</t>
+          <t>[When sending US Core Observation Occupation Profile] for … [a] current job ,systems **SHALL** omit observation.effectivePeriod.end to indicate it is ongoing.</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -39144,7 +39156,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>When the industry is known, but the occupation is not, [Servers SHALL] use the value “unknown” from the [DataAbsentReason Code System](http://hl7.org/fhir/R4/codesystem-data-absent-reason.html)</t>
+          <t>When the industry is known, but the occupation is not, systems **SHALL** use the value “unknown” from the [DataAbsentReason Code System](http://hl7.org/fhir/R4/codesystem-data-absent-reason.html)</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
@@ -39237,7 +39249,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>when the occupation is known but the industry is not, [Servers SHALL] omit the industry Observation.component</t>
+          <t>when the occupation is known but the industry is not, systems **SHALL** omit the industry Observation.component</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -39335,15 +39347,15 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H436" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>use to **SHALL**</t>
+          <t>deprecated is guidance USCDI data element cover this one.</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -39428,15 +39440,15 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H437" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>use to **SHALL**</t>
+          <t>deprecated is guidance USCDI data element cover this one.</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -40211,20 +40223,20 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>[US Core] treatment intervention preferences expressed by a patient may be documented in narrative (text) form or the result of selecting from a list of options provided by the content creator/implementer.</t>
+          <t>[US Core] treatment intervention preferences expressed by a patient **MAY** be documented in narrative (text) form or the result of selecting from a list of options provided by the content creator/implementer.</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H446" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>may to **MAY**</t>
+          <t>not a conf</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
@@ -40241,7 +40253,7 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t>When using US Core treatment preference, preferences may be documented in a narrative section or from a list of option</t>
+          <t>When using US Core treatment preference, preferences **MAY** be documented in a narrative section or from a list of option</t>
         </is>
       </c>
       <c r="O446" t="inlineStr"/>
@@ -40330,7 +40342,7 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t>When using US Core treatment preference, the preference should be supplied in a observation.valueString or extension</t>
+          <t>When using US Core treatment preference, the preference **SHOULD**be supplied in a observation.valueString or extension</t>
         </is>
       </c>
       <c r="O447" t="inlineStr"/>
@@ -40389,7 +40401,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>[US Core Vital Signs] observations **MAY**  have [component](http://hl7.org/fhir/R4/observation.html#gr-comp) observations … [see] FHIR core specification [vital signs table](http://hl7.org/fhir/R4/observation-vitalsigns.html#vitals-table) for examples</t>
+          <t>[US Core Vital Signs] observations **MAY**   have [component](http://hl7.org/fhir/R4/observation.html#gr-comp) observations … [see] FHIR core specification [vital signs table](http://hl7.org/fhir/R4/observation-vitalsigns.html#vitals-table) for examples</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
@@ -40818,7 +40830,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>Inspired oxygen therapy may be represented with [component](http://hl7.org/fhir/R4/observation.html#gr-comp) observations when measured at the same time as the pulse oximetry measurements [in the US Core Pulse Oximetry profile]</t>
+          <t>Inspired oxygen therapy **MAY** be represented with [component](http://hl7.org/fhir/R4/observation.html#gr-comp) observations when measured at the same time as the pulse oximetry measurements [in the US Core Pulse Oximetry profile]</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
@@ -40831,7 +40843,7 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>may to **MAY**</t>
+          <t xml:space="preserve">may to **MAY** </t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -40933,7 +40945,7 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t>When the patient is breathing room air, the inhaled oxygen flow rate should be 0 liters/min</t>
+          <t>When the patient is breathing room air, the inhaled oxygen flow rate **SHOULD**be 0 liters/min</t>
         </is>
       </c>
       <c r="O454" t="inlineStr"/>
@@ -40992,7 +41004,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>A pulse oximetry reading without inspired oxygen component observations may imply that the measurement was performed while the patient was breathing room air or that the inspired oxygen reading was omitted. To remove this uncertainty, the inspired oxygen [component](http://hl7.org/fhir/R4/observation.html#gr-comp) observations **SHOULD** be used [when using the US Core Pulse Oximetry profile.]</t>
+          <t>A pulse oximetry reading without inspired oxygen component observations **MAY** imply that the measurement was performed while the patient was breathing room air or that the inspired oxygen reading was omitted. To remove this uncertainty, the inspired oxygen [component](http://hl7.org/fhir/R4/observation.html#gr-comp) observations **SHOULD** be used [when using the US Core Pulse Oximetry profile.]</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
@@ -41597,7 +41609,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>The Complex [Extension] for Race ... allow[s] for one or more codes of which **MAY**  include additional codes from the detailed ethnicity ... value sets drawn from the [Race &amp; Ethnicity - CDC (CDCREC)](https://phinvads.cdc.gov/vads/ViewCodeSystem.action?id=2.16.840.1.113883.6.238) code system [when using the [US Core Race Extension] (https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-race.html)]</t>
+          <t>The Complex [Extension] for Race ... allow[s] for one or more codes of which **MAY**   include additional codes from the detailed ethnicity ... value sets drawn from the [Race &amp; Ethnicity - CDC (CDCREC)](https://phinvads.cdc.gov/vads/ViewCodeSystem.action?id=2.16.840.1.113883.6.238) code system [when using the [US Core Race Extension] (https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-race.html)]</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -41785,7 +41797,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>The Complex [Extension] for ... Ethnicity allow[s] for one or more codes of which **MAY**  include additional codes from the detailed ... race value sets drawn from the [Race &amp; Ethnicity - CDC (CDCREC)](https://phinvads.cdc.gov/vads/ViewCodeSystem.action?id=2.16.840.1.113883.6.238) code system [when using the [US Core Race Extension] (https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-race.html)]</t>
+          <t>The Complex [Extension] for ... Ethnicity allow[s] for one or more codes of which **MAY**   include additional codes from the detailed ... race value sets drawn from the [Race &amp; Ethnicity - CDC (CDCREC)](https://phinvads.cdc.gov/vads/ViewCodeSystem.action?id=2.16.840.1.113883.6.238) code system [when using the [US Core Race Extension] (https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-race.html)]</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -42045,7 +42057,7 @@
       <c r="AA466" t="inlineStr"/>
       <c r="AB466" t="inlineStr">
         <is>
-          <t>Proposal for a potentially better way to state this requirement: Certified system SHALL support Patient.deceasedDateTime and MAY support Patient.deceasedBoolean. Non certified system SHALL support at least one date type under Patient.deceased[x]</t>
+          <t>Proposal for a potentially better way to state this requirement: Certified system SHALL support Patient.deceasedDateTime and **MAY** support Patient.deceasedBoolean. Non certified system SHALL support at least one date type under Patient.deceased[x]</t>
         </is>
       </c>
       <c r="AC466" t="inlineStr"/>
@@ -42078,20 +42090,20 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>Previous name is represented by setting Patient.name.use to “old” or providing an end date in Patient.name.period or doing both</t>
+          <t>Systems **SHALL** represent *Previous name*  by setting `Patient.name.use` to "old" or providing an end date in `Patient.name.period` or doing both.</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>SHOULD</t>
+          <t>SHALL</t>
         </is>
       </c>
       <c r="H467" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>is to **SHOULD**</t>
+          <t>"is represnted by"to **SHALL**</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -42108,7 +42120,7 @@
       </c>
       <c r="N467" t="inlineStr">
         <is>
-          <t>Previous name should be represented by setting  setting Patient.name.use to “old” or providing an end date in Patient.name.period</t>
+          <t>Previous name **SHOULD**be represented by setting  setting Patient.name.use to “old” or providing an end date in Patient.name.period</t>
         </is>
       </c>
       <c r="O467" t="inlineStr"/>
@@ -42163,20 +42175,20 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>Previous address is represented by setting Patient.address.use to “old” or providing an end date in Patient.address.period or doing both.</t>
+          <t>Systems **SHALL** represent *Previous Address* by setting `Patient.address.use` to "old" or providing an end date in `Patient.address.period` or doing both.</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>SHOULD</t>
+          <t>SHALL</t>
         </is>
       </c>
       <c r="H468" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>"is represnted by"to **SHOULD**</t>
+          <t>"is represnted by"to **SHALL**</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
@@ -42193,7 +42205,7 @@
       </c>
       <c r="N468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Previous address is should be represented by setting Patient.address.use to “old” or providing an end date in Patient.address.period </t>
+          <t xml:space="preserve">Previous address is **SHOULD**be represented by setting Patient.address.use to “old” or providing an end date in Patient.address.period </t>
         </is>
       </c>
       <c r="O468" t="inlineStr"/>
@@ -42248,7 +42260,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>Communication.preferred **MAY**  designate a preferred language when multiple languages are represented</t>
+          <t>Communication.preferred **MAY**   designate a preferred language when multiple languages are represented</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -42523,7 +42535,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>[For systems participating in the ONC Health IT certification program,] this requirement [to follow the [Project US@ Technical Specification for Patient Addresses Final Version 1.0](https://asapnet.org/wp-content/uploads/2022/03/Project_US_FINAL_Technical_Specification_Version_1.0.pdf) for Patient.address.line and Patient.address.city] does not apply to historical records or documents that are exposed through FHIR-based APIs. [Organizations **MAY** choose not to use use Project US@ Technical Specification for Patient Addresses Final Version 1.0 when sending historical records]</t>
+          <t>[For systems participating in the ONC Health IT certification program,] this requirement [to follow the [Project US@ Technical Specification for Patient Addresses Final Version 1.0](https://asapnet.org/wp-content/uploads/2022/03/Project_US_FINAL_Technical_Specification_Version_1.0.pdf) for Patient.address.line and Patient.address.city]. Both certifying and non-certifying systems **MAY**  choose not to use Project US@ for historical records or documents that are not exposed through FHIR-based APIs.</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
@@ -42536,7 +42548,7 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>may to **MAY**</t>
+          <t xml:space="preserve">may to **MAY** </t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
@@ -42553,7 +42565,7 @@
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t>For organizations sending historical records and participating in the health IT certifictation program, they may choose not to follow Project US@ Technical Specification for Patient Addresses Final Version 1.0 when sending patient.address.line and patient.address.city</t>
+          <t>For organizations sending historical records and participating in the health IT certifictation program, they **MAY** choose not to follow Project US@ Technical Specification for Patient Addresses Final Version 1.0 when sending patient.address.line and patient.address.city</t>
         </is>
       </c>
       <c r="O472" t="inlineStr"/>
@@ -42729,7 +42741,7 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t>Servers that support US Core Practioner, but not US Core PractionerRole shall provide guidance on accessing provider locatin and contact information</t>
+          <t>Servers that support US Core Practitioner, but not US Core PractitionerRole **SHALL** provide guidance on accessing provider locatin and contact information</t>
         </is>
       </c>
       <c r="O474" t="inlineStr"/>
@@ -42796,7 +42808,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>Although Practitioner.address is marked as Must Support, the Server system … [**MAY** choose not to] support it if they support the US Core PractitionerRole Profile</t>
+          <t>Although Practitioner.address is marked as Must Support, the Server system **MAY**  choose not to support it if they support the US Core PractitionerRole Profile</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
@@ -42809,7 +42821,7 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>is not required to **MAY**</t>
+          <t xml:space="preserve">is not required to **MAY** </t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
@@ -42826,7 +42838,7 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t>If the system supports US Core PractionerRole, they may choose not to support practioner.address, even though it is marked as must support</t>
+          <t>If the system supports US Core PractitionerRole, they **MAY** choose not to support practioner.address, even though it is marked as must support</t>
         </is>
       </c>
       <c r="O475" t="inlineStr"/>
@@ -42889,7 +42901,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>[When using the US Core Practioner Profile] Practitioner.address … **SHALL**[be supported] if … [the Server does] not support the US Core PractitionerRole Profile</t>
+          <t>[When using the US Core Practitioner Profile] Practitioner.address … **SHALL**[be supported] if … [the Server does] not support the US Core PractitionerRole Profile</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -42915,7 +42927,7 @@
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t>When using US Core Practioner profile</t>
+          <t>When using US Core Practitioner profile</t>
         </is>
       </c>
       <c r="O476" t="inlineStr"/>
@@ -42982,7 +42994,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>The Client application **SHALL** support both [the PractionerRole profile and the Practioner.address element]</t>
+          <t>The Client application **SHALL** support both [the PractitionerRole profile and the Practitioner.address element]</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
@@ -43395,7 +43407,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>communication.preferred **MAY**  designate a preferred language when multiple languages are represented</t>
+          <t>communication.preferred **MAY**   designate a preferred language when multiple languages are represented</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
@@ -43704,7 +43716,7 @@
       </c>
       <c r="N485" t="inlineStr">
         <is>
-          <t>For organizations participating in ONC certification, Server shall support either Procedure.reasonCode or Procedure.reasonReference</t>
+          <t>For organizations participating in ONC certification, Server **SHALL** support either Procedure.reasonCode or Procedure.reasonReference</t>
         </is>
       </c>
       <c r="O485" t="inlineStr"/>
@@ -45861,7 +45873,7 @@
       </c>
       <c r="N509" t="inlineStr">
         <is>
-          <t>If Provenance.agent.who is stored as free text, then the organization source shall be provided</t>
+          <t>If Provenance.agent.who is stored as free text, then the organization source **SHALL** be provided</t>
         </is>
       </c>
       <c r="O509" t="inlineStr"/>
@@ -45924,7 +45936,7 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>If a system receives a provider in Provenance.agent.who as free text, … [upon request they] **MAY**  include the free text provider.</t>
+          <t>If a system receives a provider in Provenance.agent.who as free text, … [upon request they] **MAY**   include the free text provider.</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
@@ -45950,7 +45962,7 @@
       </c>
       <c r="N510" t="inlineStr">
         <is>
-          <t>If Provenance.agent.who is stored as free text, then the free text provider may be provided</t>
+          <t>If Provenance.agent.who is stored as free text, then the free text provider **MAY** be provided</t>
         </is>
       </c>
       <c r="O510" t="inlineStr"/>
@@ -46183,7 +46195,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>If the QuestionnaireResponse is based on a non-FHIR form [then a] … FHIR Questionnaire's questions may be omitted</t>
+          <t>If the QuestionnaireResponse is based on a non-FHIR form [then a] … FHIR Questionnaire's questions **MAY** be omitted</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
@@ -46353,7 +46365,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>The Must Support `ServiceRequest.category` is bound, at a minimum, to the [US Core ServiceRequest Category Codes](https://hl7.org/fhir/us/core/STU8/ValueSet-us-core-servicerequest-category.html), and other category codes can be used.</t>
+          <t>The Must Support `ServiceRequest.category` is bound, at a minimum, to the [US Core ServiceRequest Category Codes](https://hl7.org/fhir/us/core/STU8/ValueSet-us-core-servicerequest-category.html), and other category codes **MAY**  be used.</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
@@ -46366,7 +46378,7 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>can  to **MAY**</t>
+          <t xml:space="preserve">can  to **MAY** </t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
@@ -46750,7 +46762,7 @@
       </c>
       <c r="N519" t="inlineStr">
         <is>
-          <t>For organizations participating in ONC certification, Server shall support either Procedure.reasonCode or Procedure.reasonReference</t>
+          <t>For organizations participating in ONC certification, Server **SHALL** support either Procedure.reasonCode or Procedure.reasonReference</t>
         </is>
       </c>
       <c r="O519" t="inlineStr"/>
@@ -47191,17 +47203,17 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-specimen.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-specimen.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medication.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-specimen.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-specimen.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medication.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>Since the binding [for Specimen.type and additional USCDI elements] is [extensible](http://hl7.org/fhir/R4/terminologies.html#extensible) when a code is unavailable, just text is allowed [and conformant].</t>
+          <t>Since the binding [for Specimen.type and additional USCDI elements] is [extensible](http://hl7.org/fhir/R4/terminologies.html#extensible) when a code is unavailable, servers **MAY**  use text.</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -47214,7 +47226,7 @@
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>is allowed to **MAY**</t>
+          <t xml:space="preserve">is allowed to **MAY** </t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
@@ -47236,17 +47248,17 @@
       <c r="R524" t="inlineStr"/>
       <c r="S524" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-specimen</t>
+          <t>StructureDefinition-us-core-specimen,StructureDefinition-us-core-medication</t>
         </is>
       </c>
       <c r="T524" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U524" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Specimen: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Specimen: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medication: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V524" t="inlineStr"/>
@@ -47460,20 +47472,20 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Clients may request Specimen resources be included with the Observation or DiagnosticReport resource query.</t>
+          <t>Clients **MAY** request Specimen resources be included with the Observation or DiagnosticReport resource query.</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H527" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>may to **MAY**, change to "can" ?</t>
+          <t>not a conf</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
@@ -47647,7 +47659,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>[Clients] **MAY** support the transaction interaction</t>
+          <t>[Clients] **MAY**  support the transaction interaction</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
@@ -47736,7 +47748,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>[Clients] **MAY** support the batch interaction</t>
+          <t>[Clients] **MAY**  support the batch interaction</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -47825,7 +47837,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>[Clients] **MAY** support the search-system interaction</t>
+          <t>[Clients] **MAY**  support the search-system interaction</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -47914,7 +47926,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>[Clients] **MAY** support the history-system interaction</t>
+          <t>[Clients] **MAY**  support the history-system interaction</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -49041,7 +49053,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>[Server] **MAY** support the transaction interaction</t>
+          <t>[Server] **MAY**  support the transaction interaction</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
@@ -49122,7 +49134,7 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>[Server] **MAY** support the batch interaction</t>
+          <t>[Server] **MAY**  support the batch interaction</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
@@ -49203,7 +49215,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>[Server] **MAY** support the search-system interaction</t>
+          <t>[Server] **MAY**  support the search-system interaction</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
@@ -49284,7 +49296,7 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>[Server] **MAY** support the history-system interaction</t>
+          <t>[Server] **MAY**  support the history-system interaction</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
@@ -49476,7 +49488,7 @@
       </c>
       <c r="N550" t="inlineStr">
         <is>
-          <t>If a Server supports DocumentReference, Server should support context and contextdirect parameters</t>
+          <t>If a Server supports DocumentReference, Server **SHOULD**support context and contextdirect parameters</t>
         </is>
       </c>
       <c r="O550" t="inlineStr"/>
@@ -51730,7 +51742,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Systems **MAY**  implement the [FHIR Digital Signatures](http://hl7.org/fhir/R4/security.html#digital%20signatures)</t>
+          <t>Systems **MAY**   implement the [FHIR Digital Signatures](http://hl7.org/fhir/R4/security.html#digital%20signatures)</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
@@ -51807,7 +51819,7 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Systems **MAY**  implement the [FHIR Digital Signatures](http://hl7.org/fhir/R4/security.html#digital%20signatures)</t>
+          <t>Systems **MAY**   implement the [FHIR Digital Signatures](http://hl7.org/fhir/R4/security.html#digital%20signatures)</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
@@ -51884,7 +51896,7 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>Systems **MAY**  protect the confidentiality of data at rest via encryption and associated access controls.</t>
+          <t>Systems **MAY**   protect the confidentiality of data at rest via encryption and associated access controls.</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
@@ -51961,7 +51973,7 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>Systems **MAY**  protect the confidentiality of data at rest via encryption and associated access controls.</t>
+          <t>Systems **MAY**   protect the confidentiality of data at rest via encryption and associated access controls.</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
@@ -52626,20 +52638,20 @@
       <c r="F590" t="inlineStr">
         <is>
           <t>For querying and reading US Core Profiles, Must Support on any profile data element **SHALL** be interpreted as follows…:
-[The US Core Requesters processing of the resource instances] may result in a determination not to use the resource if the resource content does not meet business requirements.</t>
+[The US Core Requesters processing of the resource instances] **MAY** result in a determination not to use the resource if the resource content does not meet business requirements.</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>may to **MAY**</t>
+          <t>not a conf</t>
         </is>
       </c>
       <c r="J590" t="inlineStr">
@@ -53088,7 +53100,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>[I]f any sub-element is marked as *Additional USCDI* [for a complex element] and the parent element is not… [and] the parent element is represented in the structure, Certifying System **SHALL** support the sub-elements labeled as *Additional USCDI*.</t>
+          <t>[I]f any sub-element is marked as *Additional USCDI* [for a complex element] and the parent element is not… [and] the parent element is present in an instance, Certifying System **SHALL** support the sub-elements labeled as *Additional USCDI*.</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
@@ -55167,15 +55179,15 @@
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H619" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>is-required to **SHALL**</t>
+          <t>deprecated, overlaps with binding definition</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
@@ -55256,15 +55268,15 @@
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H620" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>is-required to **SHALL**</t>
+          <t>deprecated, overlaps with binding definition</t>
         </is>
       </c>
       <c r="J620" t="inlineStr">
@@ -55345,13 +55357,17 @@
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H621" t="n">
-        <v>1</v>
-      </c>
-      <c r="I621" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>deprecated, overlaps with binding definition</t>
+        </is>
+      </c>
       <c r="J621" t="inlineStr">
         <is>
           <t>Server</t>
@@ -55518,18 +55534,22 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>Certifying Systems ... **MAY** support other categories</t>
+          <t>Certifying Systems ... **MAY**  support other categories</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H623" t="n">
-        <v>5</v>
-      </c>
-      <c r="I623" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>deprecated, overlaps with binding definition</t>
+        </is>
+      </c>
       <c r="J623" t="inlineStr">
         <is>
           <t>Server</t>
@@ -55599,7 +55619,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>The `DiagnosticRequest.basedOn` element connects the DiagnosticReport to the originating order in the EHR. Systems that initiate the order **SHOULD** use this element when reporting the results.</t>
+          <t>The `DiagnosticReport.basedOn` element connects the DiagnosticReport to the originating order in the EHR. Systems that initiate the order **SHOULD** use this element when reporting the results.</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
@@ -55824,17 +55844,17 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-documentreference.html, file:///Users/ehaas/Documents/FHIR/US-Core/output/StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference.html</t>
+          <t>StructureDefinition-us-core-documentreference.html, StructureDefinition-us-core-adi-documentreference.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t xml:space="preserve"> If the referenced a document or file [referenced by `DocumentReference.content.attachment.url`]  is hosted on a Server outside the FHIR Server, it should be securely accessible using the same authorization credentials that were used to access the FHIR Server. This reduces complexity for the Client and improves the user experience.</t>
+          <t xml:space="preserve"> If the referenced document or file [referenced by `DocumentReference.content.attachment.url`]  is hosted on a Server outside the FHIR Server, it **SHOULD**be securely accessible using the same authorization credentials that were used to access the FHIR Server. This reduces complexity for the Client and improves the user experience.</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -55864,7 +55884,7 @@
       </c>
       <c r="N627" t="inlineStr">
         <is>
-          <t xml:space="preserve"> If the referenced a document or file [referenced by `DocumentReference.content.attachment.url`]  is hosted on a Server outside the FHIR Server</t>
+          <t xml:space="preserve"> If the referenced document or file [referenced by `DocumentReference.content.attachment.url`]  is hosted on a Server outside the FHIR Server</t>
         </is>
       </c>
       <c r="O627" t="inlineStr"/>
@@ -55873,12 +55893,18 @@
       <c r="R627" t="inlineStr"/>
       <c r="S627" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference</t>
-        </is>
-      </c>
-      <c r="T627" t="inlineStr"/>
-      <c r="U627" t="e">
-        <v>#VALUE!</v>
+          <t>StructureDefinition-us-core-documentreference,StructureDefinition-us-core-adi-documentreference</t>
+        </is>
+      </c>
+      <c r="T627" t="inlineStr">
+        <is>
+          <t>profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="U627" t="inlineStr">
+        <is>
+          <t>Structuredefinition-Us-Core-Documentreference: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Adi-Documentreference: Profile-Specific-Implementation-Guidance</t>
+        </is>
       </c>
       <c r="V627" t="inlineStr"/>
       <c r="W627" t="inlineStr"/>
@@ -56006,7 +56032,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>There is no guarantee that vaccine lot numbers are globally unique, and they are not recommended for matching or de-duplication across systems unless used with other data elements such as a vaccine product code, manufacturer code, or date of administration. Implementers **MAY** communicate the `Immunization.manufacturer` to ensure global uniqueness to lot numbers.</t>
+          <t>There is no guarantee that vaccine lot numbers are globally unique, and they are not recommended for matching or de-duplication across systems unless used with other data elements such as a vaccine product code, manufacturer code, or date of administration. Implementers **MAY**  communicate the `Immunization.manufacturer` to ensure global uniqueness to lot numbers.</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
@@ -56589,7 +56615,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>[For the US Core Observation Screening Assessment Profile,] Certifying Systems **MAY** support other codes.</t>
+          <t>[For the US Core Observation Screening Assessment Profile,] Certifying Systems **MAY**  support other codes.</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -56814,30 +56840,30 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-patient.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-patient.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-encounter.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-patient.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-patient.html#profile-specific-implementation-guidance, StructureDefinition-us-core-encounter.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>Servers can use the [US Core Interpreter Needed Extension](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-interpreter-needed.html) on [the [US Core Patient Profile](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-patient.html)] or the [US Core Encounter Profile](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-encounter.html) to communicate whether a patient needs an interpreter.</t>
+          <t>Servers **SHOULD** use the [US Core Interpreter Needed Extension](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-interpreter-needed.html) on [the [US Core Patient Profile](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-patient.html)] or the [US Core Encounter Profile](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-encounter.html) to communicate whether a patient needs an interpreter.</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="H639" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I639" t="inlineStr">
         <is>
-          <t>can use to ""MAY**</t>
+          <t>canto SHOULD</t>
         </is>
       </c>
       <c r="J639" t="inlineStr">
@@ -56859,17 +56885,17 @@
       <c r="R639" t="inlineStr"/>
       <c r="S639" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-patient</t>
+          <t>StructureDefinition-us-core-patient,StructureDefinition-us-core-encounter</t>
         </is>
       </c>
       <c r="T639" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U639" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Patient: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Patient: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Encounter: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V639" t="inlineStr"/>
@@ -57831,7 +57857,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>[For [US Core Simple Observation Profile](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-simple-observation.html), ]Certifying Systems ... **MAY** support other categories [in addition to  [US Core Screening Assessment Observation Category codes](https://hl7.org/fhir/us/core/STU8/ValueSet-us-core-screening-assessment-observation-category.html) and  [US Core Simple Observation Category codes](https://hl7.org/fhir/us/core/STU8/ValueSet-us-core-simple-observation-category.html)].</t>
+          <t>[For [US Core Simple Observation Profile](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-simple-observation.html), ]Certifying Systems ... **MAY**  support other categories [in addition to  [US Core Screening Assessment Observation Category codes](https://hl7.org/fhir/us/core/STU8/ValueSet-us-core-screening-assessment-observation-category.html) and  [US Core Simple Observation Category codes](https://hl7.org/fhir/us/core/STU8/ValueSet-us-core-simple-observation-category.html)].</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -58700,11 +58726,7 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A661" t="inlineStr"/>
       <c r="B661" t="n">
         <v>873</v>
       </c>
@@ -58797,11 +58819,7 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A662" t="inlineStr"/>
       <c r="B662" t="n">
         <v>874</v>
       </c>
@@ -58894,11 +58912,7 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A663" t="inlineStr"/>
       <c r="B663" t="n">
         <v>875</v>
       </c>
@@ -58991,11 +59005,7 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A664" t="inlineStr"/>
       <c r="B664" t="n">
         <v>876</v>
       </c>
@@ -59088,11 +59098,7 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A665" t="inlineStr"/>
       <c r="B665" t="n">
         <v>877</v>
       </c>
@@ -59181,11 +59187,7 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A666" t="inlineStr"/>
       <c r="B666" t="n">
         <v>878</v>
       </c>
@@ -59278,11 +59280,7 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A667" t="inlineStr"/>
       <c r="B667" t="n">
         <v>879</v>
       </c>
@@ -59371,11 +59369,7 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A668" t="inlineStr"/>
       <c r="B668" t="n">
         <v>880</v>
       </c>
@@ -59468,11 +59462,7 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A669" t="inlineStr"/>
       <c r="B669" t="n">
         <v>881</v>
       </c>
@@ -59559,11 +59549,7 @@
       </c>
     </row>
     <row r="670">
-      <c r="A670" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A670" t="inlineStr"/>
       <c r="B670" t="n">
         <v>882</v>
       </c>
@@ -59650,11 +59636,7 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A671" t="inlineStr"/>
       <c r="B671" t="n">
         <v>883</v>
       </c>
@@ -59743,11 +59725,7 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A672" t="inlineStr"/>
       <c r="B672" t="n">
         <v>884</v>
       </c>
@@ -59828,11 +59806,7 @@
       <c r="AE672" t="inlineStr"/>
     </row>
     <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A673" t="inlineStr"/>
       <c r="B673" t="n">
         <v>885</v>
       </c>
@@ -59909,11 +59883,7 @@
       <c r="AE673" t="inlineStr"/>
     </row>
     <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A674" t="inlineStr"/>
       <c r="B674" t="n">
         <v>886</v>
       </c>
@@ -59986,11 +59956,7 @@
       <c r="AE674" t="inlineStr"/>
     </row>
     <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A675" t="inlineStr"/>
       <c r="B675" t="n">
         <v>887</v>
       </c>
@@ -60063,11 +60029,7 @@
       <c r="AE675" t="inlineStr"/>
     </row>
     <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A676" t="inlineStr"/>
       <c r="B676" t="n">
         <v>888</v>
       </c>
@@ -60140,11 +60102,7 @@
       <c r="AE676" t="inlineStr"/>
     </row>
     <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A677" t="inlineStr"/>
       <c r="B677" t="n">
         <v>889</v>
       </c>
@@ -60217,11 +60175,7 @@
       <c r="AE677" t="inlineStr"/>
     </row>
     <row r="678">
-      <c r="A678" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A678" t="inlineStr"/>
       <c r="B678" t="n">
         <v>890</v>
       </c>
@@ -60294,11 +60248,7 @@
       <c r="AE678" t="inlineStr"/>
     </row>
     <row r="679">
-      <c r="A679" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A679" t="inlineStr"/>
       <c r="B679" t="n">
         <v>891</v>
       </c>
@@ -60371,11 +60321,7 @@
       <c r="AE679" t="inlineStr"/>
     </row>
     <row r="680">
-      <c r="A680" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A680" t="inlineStr"/>
       <c r="B680" t="n">
         <v>892</v>
       </c>
@@ -60448,11 +60394,7 @@
       <c r="AE680" t="inlineStr"/>
     </row>
     <row r="681">
-      <c r="A681" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A681" t="inlineStr"/>
       <c r="B681" t="n">
         <v>893</v>
       </c>
@@ -60478,15 +60420,15 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H681" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>can  to ""MAY**</t>
+          <t>keep as can deprecated</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
@@ -60529,11 +60471,7 @@
       <c r="AE681" t="inlineStr"/>
     </row>
     <row r="682">
-      <c r="A682" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A682" t="inlineStr"/>
       <c r="B682" t="n">
         <v>894</v>
       </c>
@@ -60606,11 +60544,7 @@
       <c r="AE682" t="inlineStr"/>
     </row>
     <row r="683">
-      <c r="A683" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A683" t="inlineStr"/>
       <c r="B683" t="n">
         <v>895</v>
       </c>
@@ -60683,11 +60617,7 @@
       <c r="AE683" t="inlineStr"/>
     </row>
     <row r="684">
-      <c r="A684" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A684" t="inlineStr"/>
       <c r="B684" t="n">
         <v>896</v>
       </c>
@@ -60760,11 +60690,7 @@
       <c r="AE684" t="inlineStr"/>
     </row>
     <row r="685">
-      <c r="A685" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A685" t="inlineStr"/>
       <c r="B685" t="n">
         <v>897</v>
       </c>
@@ -60837,11 +60763,7 @@
       <c r="AE685" t="inlineStr"/>
     </row>
     <row r="686">
-      <c r="A686" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A686" t="inlineStr"/>
       <c r="B686" t="n">
         <v>898</v>
       </c>
@@ -60862,7 +60784,7 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>For data not captured by the system transmitting the information, ....the system **MAY** provide the existing code or the free text, and a high-level abstract code, such as the SNOMED CT code "71388002"(Procedure), to remain conformant with the extensible binding.</t>
+          <t>For data not captured by the system transmitting the information, ....the system **MAY**  provide the existing code or the free text, and a high-level abstract code, such as the SNOMED CT code "71388002"(Procedure), to remain conformant with the extensible binding.</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -60914,11 +60836,7 @@
       <c r="AE686" t="inlineStr"/>
     </row>
     <row r="687">
-      <c r="A687" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A687" t="inlineStr"/>
       <c r="B687" t="n">
         <v>899</v>
       </c>
@@ -60939,7 +60857,7 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>To represent the patient and provider attestation metadata, the *optional* DocumentReference Attestor R5 Extension ... **SHOULD** be use</t>
+          <t>To represent the patient and provider attestation metadata, the optional DocumentReference Attestor R5 Extension defined in the US Core DocumentReference Profile **SHOULD** be used</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
@@ -60991,11 +60909,7 @@
       <c r="AE687" t="inlineStr"/>
     </row>
     <row r="688">
-      <c r="A688" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A688" t="inlineStr"/>
       <c r="B688" t="n">
         <v>900</v>
       </c>
@@ -61068,11 +60982,7 @@
       <c r="AE688" t="inlineStr"/>
     </row>
     <row r="689">
-      <c r="A689" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A689" t="inlineStr"/>
       <c r="B689" t="n">
         <v>901</v>
       </c>
@@ -61093,7 +61003,7 @@
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>The Service Delivery Location Role Type value set is inherited from the base resource, and, although its binding strength is [extensible](http://hl7.org/fhir/R4/terminologies.html#extensible) in the base resource, US Core implementers **MAY** treat it as [preferred](http://hl7.org/fhir/R4/terminologies.html#preferred).</t>
+          <t>The Service Delivery Location Role Type value set is inherited from the base resource, and, although its binding strength is [extensible](http://hl7.org/fhir/R4/terminologies.html#extensible) in the base resource, US Core implementers **MAY**  treat it as [preferred](http://hl7.org/fhir/R4/terminologies.html#preferred).</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
@@ -61145,11 +61055,7 @@
       <c r="AE689" t="inlineStr"/>
     </row>
     <row r="690">
-      <c r="A690" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A690" t="inlineStr"/>
       <c r="B690" t="n">
         <v>902</v>
       </c>
@@ -61170,7 +61076,7 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>Healthcare Service Location Codes (HSLOC) and SNOMED-CT Healthcare Facility Type value sets meet the USCDI applicable vocabulary standard for the Encounter Location Data Element. Certifying Systems **MAY** use a code from either vocabulary.</t>
+          <t>Healthcare Service Location Codes (HSLOC) and SNOMED-CT Healthcare Facility Type value sets meet the USCDI applicable vocabulary standard for the Encounter Location Data Element. Certifying Systems **MAY**  use a code from either vocabulary.</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -61226,11 +61132,7 @@
       <c r="AE690" t="inlineStr"/>
     </row>
     <row r="691">
-      <c r="A691" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A691" t="inlineStr"/>
       <c r="B691" t="n">
         <v>903</v>
       </c>
@@ -61303,11 +61205,7 @@
       <c r="AE691" t="inlineStr"/>
     </row>
     <row r="692">
-      <c r="A692" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A692" t="inlineStr"/>
       <c r="B692" t="n">
         <v>904</v>
       </c>
@@ -61380,11 +61278,7 @@
       <c r="AE692" t="inlineStr"/>
     </row>
     <row r="693">
-      <c r="A693" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A693" t="inlineStr"/>
       <c r="B693" t="n">
         <v>905</v>
       </c>
@@ -61405,7 +61299,7 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>the US Core ServiceRequest Profile **MAY** be used to represent a derived "actionable" order based on a portable Medical Order(PMO).</t>
+          <t>the US Core ServiceRequest Profile **MAY**  be used to represent a derived "actionable" order based on a portable Medical Order(PMO).</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
@@ -61457,11 +61351,7 @@
       <c r="AE693" t="inlineStr"/>
     </row>
     <row r="694">
-      <c r="A694" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A694" t="inlineStr"/>
       <c r="B694" t="n">
         <v>906</v>
       </c>
@@ -61534,11 +61424,7 @@
       <c r="AE694" t="inlineStr"/>
     </row>
     <row r="695">
-      <c r="A695" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A695" t="inlineStr"/>
       <c r="B695" t="n">
         <v>907</v>
       </c>
@@ -61611,11 +61497,7 @@
       <c r="AE695" t="inlineStr"/>
     </row>
     <row r="696">
-      <c r="A696" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A696" t="inlineStr"/>
       <c r="B696" t="n">
         <v>908</v>
       </c>
@@ -61688,11 +61570,7 @@
       <c r="AE696" t="inlineStr"/>
     </row>
     <row r="697">
-      <c r="A697" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A697" t="inlineStr"/>
       <c r="B697" t="n">
         <v>909</v>
       </c>
@@ -61768,26 +61646,78 @@
     </row>
     <row r="698">
       <c r="A698" t="inlineStr"/>
-      <c r="B698" t="inlineStr"/>
-      <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr"/>
-      <c r="E698" t="inlineStr"/>
-      <c r="F698" t="inlineStr"/>
-      <c r="G698" t="inlineStr"/>
-      <c r="H698" t="inlineStr"/>
-      <c r="I698" t="inlineStr"/>
-      <c r="J698" t="inlineStr"/>
-      <c r="K698" t="inlineStr"/>
+      <c r="B698" t="n">
+        <v>910</v>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>CONF-0910</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-patient.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-encounter.html#profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-patient.html#profile-specific-implementation-guidance, StructureDefinition-us-core-encounter.html#profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Servers **SHALL** use the [US Core Interpreter Needed Extension](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-interpreter-needed.html) on [the [US Core Patient Profile](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-patient.html)] or the [US Core Encounter Profile](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-encounter.html) to communicate whether a patient needs an interpreter.</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="H698" t="n">
+        <v>1</v>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>canto SHALL</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr"/>
-      <c r="M698" t="inlineStr"/>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="N698" t="inlineStr"/>
       <c r="O698" t="inlineStr"/>
       <c r="P698" t="inlineStr"/>
       <c r="Q698" t="inlineStr"/>
       <c r="R698" t="inlineStr"/>
-      <c r="S698" t="inlineStr"/>
-      <c r="T698" t="inlineStr"/>
-      <c r="U698" t="inlineStr"/>
+      <c r="S698" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-patient,StructureDefinition-us-core-encounter</t>
+        </is>
+      </c>
+      <c r="T698" t="inlineStr">
+        <is>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="U698" t="inlineStr">
+        <is>
+          <t>Structuredefinition-Us-Core-Patient: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Encounter: Profile-Specific-Implementation-Guidance</t>
+        </is>
+      </c>
       <c r="V698" t="inlineStr"/>
       <c r="W698" t="inlineStr"/>
       <c r="X698" t="inlineStr"/>
@@ -61801,26 +61731,70 @@
     </row>
     <row r="699">
       <c r="A699" t="inlineStr"/>
-      <c r="B699" t="inlineStr"/>
-      <c r="C699" t="inlineStr"/>
-      <c r="D699" t="inlineStr"/>
-      <c r="E699" t="inlineStr"/>
-      <c r="F699" t="inlineStr"/>
-      <c r="G699" t="inlineStr"/>
-      <c r="H699" t="inlineStr"/>
+      <c r="B699" t="n">
+        <v>911</v>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>CONF-0911</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-servicerequest.html#profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-servicerequest.html#profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>API consumers **MAY**  query by category when accessing patient information.</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="H699" t="n">
+        <v>5</v>
+      </c>
       <c r="I699" t="inlineStr"/>
-      <c r="J699" t="inlineStr"/>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
       <c r="K699" t="inlineStr"/>
       <c r="L699" t="inlineStr"/>
-      <c r="M699" t="inlineStr"/>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="N699" t="inlineStr"/>
       <c r="O699" t="inlineStr"/>
       <c r="P699" t="inlineStr"/>
       <c r="Q699" t="inlineStr"/>
       <c r="R699" t="inlineStr"/>
-      <c r="S699" t="inlineStr"/>
-      <c r="T699" t="inlineStr"/>
-      <c r="U699" t="inlineStr"/>
+      <c r="S699" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-servicerequest</t>
+        </is>
+      </c>
+      <c r="T699" t="inlineStr">
+        <is>
+          <t>profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="U699" t="inlineStr">
+        <is>
+          <t>Structuredefinition-Us-Core-Servicerequest: Profile-Specific-Implementation-Guidance</t>
+        </is>
+      </c>
       <c r="V699" t="inlineStr"/>
       <c r="W699" t="inlineStr"/>
       <c r="X699" t="inlineStr"/>
@@ -61834,26 +61808,70 @@
     </row>
     <row r="700">
       <c r="A700" t="inlineStr"/>
-      <c r="B700" t="inlineStr"/>
-      <c r="C700" t="inlineStr"/>
-      <c r="D700" t="inlineStr"/>
-      <c r="E700" t="inlineStr"/>
-      <c r="F700" t="inlineStr"/>
-      <c r="G700" t="inlineStr"/>
-      <c r="H700" t="inlineStr"/>
+      <c r="B700" t="n">
+        <v>912</v>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>CONF-0912</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>https://build.fhir.org/ig/HL7/US-Core/terminology.html#us-core-valueset-and-codesystem-versions</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>terminology.html#us-core-valueset-and-codesystem-versions</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>When implementing US Core, implementers **SHOULD** use the published versions or later versions of the value sets and code systems.</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
+        </is>
+      </c>
+      <c r="H700" t="n">
+        <v>3</v>
+      </c>
       <c r="I700" t="inlineStr"/>
-      <c r="J700" t="inlineStr"/>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
       <c r="K700" t="inlineStr"/>
       <c r="L700" t="inlineStr"/>
-      <c r="M700" t="inlineStr"/>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="N700" t="inlineStr"/>
       <c r="O700" t="inlineStr"/>
       <c r="P700" t="inlineStr"/>
       <c r="Q700" t="inlineStr"/>
       <c r="R700" t="inlineStr"/>
-      <c r="S700" t="inlineStr"/>
-      <c r="T700" t="inlineStr"/>
-      <c r="U700" t="inlineStr"/>
+      <c r="S700" t="inlineStr">
+        <is>
+          <t>terminology</t>
+        </is>
+      </c>
+      <c r="T700" t="inlineStr">
+        <is>
+          <t>us-core-valueset-and-codesystem-versions</t>
+        </is>
+      </c>
+      <c r="U700" t="inlineStr">
+        <is>
+          <t>Terminology: Us-Core-Valueset-And-Codesystem-Versions</t>
+        </is>
+      </c>
       <c r="V700" t="inlineStr"/>
       <c r="W700" t="inlineStr"/>
       <c r="X700" t="inlineStr"/>
@@ -61867,26 +61885,70 @@
     </row>
     <row r="701">
       <c r="A701" t="inlineStr"/>
-      <c r="B701" t="inlineStr"/>
-      <c r="C701" t="inlineStr"/>
-      <c r="D701" t="inlineStr"/>
-      <c r="E701" t="inlineStr"/>
-      <c r="F701" t="inlineStr"/>
-      <c r="G701" t="inlineStr"/>
-      <c r="H701" t="inlineStr"/>
+      <c r="B701" t="n">
+        <v>913</v>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>CONF-0913</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>https://build.fhir.org/ig/HL7/US-Core/terminology.html#us-core-valueset-and-codesystem-versions</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>terminology.html#us-core-valueset-and-codesystem-versions</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>In some cases, [when implementing US Core]  implementers **MAY**  need to use terminology from earlier versions to preserve legacy data.</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="H701" t="n">
+        <v>5</v>
+      </c>
       <c r="I701" t="inlineStr"/>
-      <c r="J701" t="inlineStr"/>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
       <c r="K701" t="inlineStr"/>
       <c r="L701" t="inlineStr"/>
-      <c r="M701" t="inlineStr"/>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="N701" t="inlineStr"/>
       <c r="O701" t="inlineStr"/>
       <c r="P701" t="inlineStr"/>
       <c r="Q701" t="inlineStr"/>
       <c r="R701" t="inlineStr"/>
-      <c r="S701" t="inlineStr"/>
-      <c r="T701" t="inlineStr"/>
-      <c r="U701" t="inlineStr"/>
+      <c r="S701" t="inlineStr">
+        <is>
+          <t>terminology</t>
+        </is>
+      </c>
+      <c r="T701" t="inlineStr">
+        <is>
+          <t>us-core-valueset-and-codesystem-versions</t>
+        </is>
+      </c>
+      <c r="U701" t="inlineStr">
+        <is>
+          <t>Terminology: Us-Core-Valueset-And-Codesystem-Versions</t>
+        </is>
+      </c>
       <c r="V701" t="inlineStr"/>
       <c r="W701" t="inlineStr"/>
       <c r="X701" t="inlineStr"/>
@@ -61900,26 +61962,74 @@
     </row>
     <row r="702">
       <c r="A702" t="inlineStr"/>
-      <c r="B702" t="inlineStr"/>
-      <c r="C702" t="inlineStr"/>
-      <c r="D702" t="inlineStr"/>
-      <c r="E702" t="inlineStr"/>
-      <c r="F702" t="inlineStr"/>
-      <c r="G702" t="inlineStr"/>
-      <c r="H702" t="inlineStr"/>
-      <c r="I702" t="inlineStr"/>
-      <c r="J702" t="inlineStr"/>
+      <c r="B702" t="n">
+        <v>914</v>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>CONF-0914</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-patient.html#profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-patient.html#profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Systems **SHALL** represent *Suffix* using the `Patient.name.suffix` element.</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="H702" t="n">
+        <v>1</v>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>is represented by to SHALL</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
       <c r="K702" t="inlineStr"/>
       <c r="L702" t="inlineStr"/>
-      <c r="M702" t="inlineStr"/>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="N702" t="inlineStr"/>
       <c r="O702" t="inlineStr"/>
       <c r="P702" t="inlineStr"/>
       <c r="Q702" t="inlineStr"/>
       <c r="R702" t="inlineStr"/>
-      <c r="S702" t="inlineStr"/>
-      <c r="T702" t="inlineStr"/>
-      <c r="U702" t="inlineStr"/>
+      <c r="S702" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-patient</t>
+        </is>
+      </c>
+      <c r="T702" t="inlineStr">
+        <is>
+          <t>profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="U702" t="inlineStr">
+        <is>
+          <t>Structuredefinition-Us-Core-Patient: Profile-Specific-Implementation-Guidance</t>
+        </is>
+      </c>
       <c r="V702" t="inlineStr"/>
       <c r="W702" t="inlineStr"/>
       <c r="X702" t="inlineStr"/>
@@ -61933,26 +62043,70 @@
     </row>
     <row r="703">
       <c r="A703" t="inlineStr"/>
-      <c r="B703" t="inlineStr"/>
-      <c r="C703" t="inlineStr"/>
-      <c r="D703" t="inlineStr"/>
-      <c r="E703" t="inlineStr"/>
-      <c r="F703" t="inlineStr"/>
-      <c r="G703" t="inlineStr"/>
-      <c r="H703" t="inlineStr"/>
+      <c r="B703" t="n">
+        <v>915</v>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>CONF-0915</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>file:///Users/ehaas/Documents/FHIR/US-Core/output/general-requirements.html#conforming-to-us-core</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>general-requirements.html#conforming-to-us-core</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Profile Only Support: Systems **MAY** support *only* the US Core Profiles to represent clinical information.</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="H703" t="n">
+        <v>5</v>
+      </c>
       <c r="I703" t="inlineStr"/>
-      <c r="J703" t="inlineStr"/>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
       <c r="K703" t="inlineStr"/>
       <c r="L703" t="inlineStr"/>
-      <c r="M703" t="inlineStr"/>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="N703" t="inlineStr"/>
       <c r="O703" t="inlineStr"/>
       <c r="P703" t="inlineStr"/>
       <c r="Q703" t="inlineStr"/>
       <c r="R703" t="inlineStr"/>
-      <c r="S703" t="inlineStr"/>
-      <c r="T703" t="inlineStr"/>
-      <c r="U703" t="inlineStr"/>
+      <c r="S703" t="inlineStr">
+        <is>
+          <t>general-requirements</t>
+        </is>
+      </c>
+      <c r="T703" t="inlineStr">
+        <is>
+          <t>conforming-to-us-core</t>
+        </is>
+      </c>
+      <c r="U703" t="inlineStr">
+        <is>
+          <t>General-Requirements: Conforming-To-Us-Core</t>
+        </is>
+      </c>
       <c r="V703" t="inlineStr"/>
       <c r="W703" t="inlineStr"/>
       <c r="X703" t="inlineStr"/>
@@ -61966,26 +62120,70 @@
     </row>
     <row r="704">
       <c r="A704" t="inlineStr"/>
-      <c r="B704" t="inlineStr"/>
-      <c r="C704" t="inlineStr"/>
-      <c r="D704" t="inlineStr"/>
-      <c r="E704" t="inlineStr"/>
-      <c r="F704" t="inlineStr"/>
-      <c r="G704" t="inlineStr"/>
-      <c r="H704" t="inlineStr"/>
+      <c r="B704" t="n">
+        <v>916</v>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>CONF-0916</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>file:///Users/ehaas/Documents/FHIR/US-Core/output/general-requirements.html#conforming-to-us-core</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>general-requirements.html#conforming-to-us-core</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Profile Support + Interaction Support: Systems **MAY** support *both* the US Core Profile content structure *and* the RESTful interactions defined for a resource.</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="H704" t="n">
+        <v>5</v>
+      </c>
       <c r="I704" t="inlineStr"/>
-      <c r="J704" t="inlineStr"/>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
       <c r="K704" t="inlineStr"/>
       <c r="L704" t="inlineStr"/>
-      <c r="M704" t="inlineStr"/>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="N704" t="inlineStr"/>
       <c r="O704" t="inlineStr"/>
       <c r="P704" t="inlineStr"/>
       <c r="Q704" t="inlineStr"/>
       <c r="R704" t="inlineStr"/>
-      <c r="S704" t="inlineStr"/>
-      <c r="T704" t="inlineStr"/>
-      <c r="U704" t="inlineStr"/>
+      <c r="S704" t="inlineStr">
+        <is>
+          <t>general-requirements</t>
+        </is>
+      </c>
+      <c r="T704" t="inlineStr">
+        <is>
+          <t>conforming-to-us-core</t>
+        </is>
+      </c>
+      <c r="U704" t="inlineStr">
+        <is>
+          <t>General-Requirements: Conforming-To-Us-Core</t>
+        </is>
+      </c>
       <c r="V704" t="inlineStr"/>
       <c r="W704" t="inlineStr"/>
       <c r="X704" t="inlineStr"/>
@@ -62030,6 +62228,237 @@
       <c r="AD705" t="inlineStr"/>
       <c r="AE705" t="inlineStr"/>
     </row>
+    <row r="706">
+      <c r="A706" t="inlineStr"/>
+      <c r="B706" t="inlineStr"/>
+      <c r="C706" t="inlineStr"/>
+      <c r="D706" t="inlineStr"/>
+      <c r="E706" t="inlineStr"/>
+      <c r="F706" t="inlineStr"/>
+      <c r="G706" t="inlineStr"/>
+      <c r="H706" t="inlineStr"/>
+      <c r="I706" t="inlineStr"/>
+      <c r="J706" t="inlineStr"/>
+      <c r="K706" t="inlineStr"/>
+      <c r="L706" t="inlineStr"/>
+      <c r="M706" t="inlineStr"/>
+      <c r="N706" t="inlineStr"/>
+      <c r="O706" t="inlineStr"/>
+      <c r="P706" t="inlineStr"/>
+      <c r="Q706" t="inlineStr"/>
+      <c r="R706" t="inlineStr"/>
+      <c r="S706" t="inlineStr"/>
+      <c r="T706" t="inlineStr"/>
+      <c r="U706" t="inlineStr"/>
+      <c r="V706" t="inlineStr"/>
+      <c r="W706" t="inlineStr"/>
+      <c r="X706" t="inlineStr"/>
+      <c r="Y706" t="inlineStr"/>
+      <c r="Z706" t="inlineStr"/>
+      <c r="AA706" t="inlineStr"/>
+      <c r="AB706" t="inlineStr"/>
+      <c r="AC706" t="inlineStr"/>
+      <c r="AD706" t="inlineStr"/>
+      <c r="AE706" t="inlineStr"/>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr"/>
+      <c r="B707" t="inlineStr"/>
+      <c r="C707" t="inlineStr"/>
+      <c r="D707" t="inlineStr"/>
+      <c r="E707" t="inlineStr"/>
+      <c r="F707" t="inlineStr"/>
+      <c r="G707" t="inlineStr"/>
+      <c r="H707" t="inlineStr"/>
+      <c r="I707" t="inlineStr"/>
+      <c r="J707" t="inlineStr"/>
+      <c r="K707" t="inlineStr"/>
+      <c r="L707" t="inlineStr"/>
+      <c r="M707" t="inlineStr"/>
+      <c r="N707" t="inlineStr"/>
+      <c r="O707" t="inlineStr"/>
+      <c r="P707" t="inlineStr"/>
+      <c r="Q707" t="inlineStr"/>
+      <c r="R707" t="inlineStr"/>
+      <c r="S707" t="inlineStr"/>
+      <c r="T707" t="inlineStr"/>
+      <c r="U707" t="inlineStr"/>
+      <c r="V707" t="inlineStr"/>
+      <c r="W707" t="inlineStr"/>
+      <c r="X707" t="inlineStr"/>
+      <c r="Y707" t="inlineStr"/>
+      <c r="Z707" t="inlineStr"/>
+      <c r="AA707" t="inlineStr"/>
+      <c r="AB707" t="inlineStr"/>
+      <c r="AC707" t="inlineStr"/>
+      <c r="AD707" t="inlineStr"/>
+      <c r="AE707" t="inlineStr"/>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr"/>
+      <c r="B708" t="inlineStr"/>
+      <c r="C708" t="inlineStr"/>
+      <c r="D708" t="inlineStr"/>
+      <c r="E708" t="inlineStr"/>
+      <c r="F708" t="inlineStr"/>
+      <c r="G708" t="inlineStr"/>
+      <c r="H708" t="inlineStr"/>
+      <c r="I708" t="inlineStr"/>
+      <c r="J708" t="inlineStr"/>
+      <c r="K708" t="inlineStr"/>
+      <c r="L708" t="inlineStr"/>
+      <c r="M708" t="inlineStr"/>
+      <c r="N708" t="inlineStr"/>
+      <c r="O708" t="inlineStr"/>
+      <c r="P708" t="inlineStr"/>
+      <c r="Q708" t="inlineStr"/>
+      <c r="R708" t="inlineStr"/>
+      <c r="S708" t="inlineStr"/>
+      <c r="T708" t="inlineStr"/>
+      <c r="U708" t="inlineStr"/>
+      <c r="V708" t="inlineStr"/>
+      <c r="W708" t="inlineStr"/>
+      <c r="X708" t="inlineStr"/>
+      <c r="Y708" t="inlineStr"/>
+      <c r="Z708" t="inlineStr"/>
+      <c r="AA708" t="inlineStr"/>
+      <c r="AB708" t="inlineStr"/>
+      <c r="AC708" t="inlineStr"/>
+      <c r="AD708" t="inlineStr"/>
+      <c r="AE708" t="inlineStr"/>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr"/>
+      <c r="B709" t="inlineStr"/>
+      <c r="C709" t="inlineStr"/>
+      <c r="D709" t="inlineStr"/>
+      <c r="E709" t="inlineStr"/>
+      <c r="F709" t="inlineStr"/>
+      <c r="G709" t="inlineStr"/>
+      <c r="H709" t="inlineStr"/>
+      <c r="I709" t="inlineStr"/>
+      <c r="J709" t="inlineStr"/>
+      <c r="K709" t="inlineStr"/>
+      <c r="L709" t="inlineStr"/>
+      <c r="M709" t="inlineStr"/>
+      <c r="N709" t="inlineStr"/>
+      <c r="O709" t="inlineStr"/>
+      <c r="P709" t="inlineStr"/>
+      <c r="Q709" t="inlineStr"/>
+      <c r="R709" t="inlineStr"/>
+      <c r="S709" t="inlineStr"/>
+      <c r="T709" t="inlineStr"/>
+      <c r="U709" t="inlineStr"/>
+      <c r="V709" t="inlineStr"/>
+      <c r="W709" t="inlineStr"/>
+      <c r="X709" t="inlineStr"/>
+      <c r="Y709" t="inlineStr"/>
+      <c r="Z709" t="inlineStr"/>
+      <c r="AA709" t="inlineStr"/>
+      <c r="AB709" t="inlineStr"/>
+      <c r="AC709" t="inlineStr"/>
+      <c r="AD709" t="inlineStr"/>
+      <c r="AE709" t="inlineStr"/>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr"/>
+      <c r="B710" t="inlineStr"/>
+      <c r="C710" t="inlineStr"/>
+      <c r="D710" t="inlineStr"/>
+      <c r="E710" t="inlineStr"/>
+      <c r="F710" t="inlineStr"/>
+      <c r="G710" t="inlineStr"/>
+      <c r="H710" t="inlineStr"/>
+      <c r="I710" t="inlineStr"/>
+      <c r="J710" t="inlineStr"/>
+      <c r="K710" t="inlineStr"/>
+      <c r="L710" t="inlineStr"/>
+      <c r="M710" t="inlineStr"/>
+      <c r="N710" t="inlineStr"/>
+      <c r="O710" t="inlineStr"/>
+      <c r="P710" t="inlineStr"/>
+      <c r="Q710" t="inlineStr"/>
+      <c r="R710" t="inlineStr"/>
+      <c r="S710" t="inlineStr"/>
+      <c r="T710" t="inlineStr"/>
+      <c r="U710" t="inlineStr"/>
+      <c r="V710" t="inlineStr"/>
+      <c r="W710" t="inlineStr"/>
+      <c r="X710" t="inlineStr"/>
+      <c r="Y710" t="inlineStr"/>
+      <c r="Z710" t="inlineStr"/>
+      <c r="AA710" t="inlineStr"/>
+      <c r="AB710" t="inlineStr"/>
+      <c r="AC710" t="inlineStr"/>
+      <c r="AD710" t="inlineStr"/>
+      <c r="AE710" t="inlineStr"/>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr"/>
+      <c r="B711" t="inlineStr"/>
+      <c r="C711" t="inlineStr"/>
+      <c r="D711" t="inlineStr"/>
+      <c r="E711" t="inlineStr"/>
+      <c r="F711" t="inlineStr"/>
+      <c r="G711" t="inlineStr"/>
+      <c r="H711" t="inlineStr"/>
+      <c r="I711" t="inlineStr"/>
+      <c r="J711" t="inlineStr"/>
+      <c r="K711" t="inlineStr"/>
+      <c r="L711" t="inlineStr"/>
+      <c r="M711" t="inlineStr"/>
+      <c r="N711" t="inlineStr"/>
+      <c r="O711" t="inlineStr"/>
+      <c r="P711" t="inlineStr"/>
+      <c r="Q711" t="inlineStr"/>
+      <c r="R711" t="inlineStr"/>
+      <c r="S711" t="inlineStr"/>
+      <c r="T711" t="inlineStr"/>
+      <c r="U711" t="inlineStr"/>
+      <c r="V711" t="inlineStr"/>
+      <c r="W711" t="inlineStr"/>
+      <c r="X711" t="inlineStr"/>
+      <c r="Y711" t="inlineStr"/>
+      <c r="Z711" t="inlineStr"/>
+      <c r="AA711" t="inlineStr"/>
+      <c r="AB711" t="inlineStr"/>
+      <c r="AC711" t="inlineStr"/>
+      <c r="AD711" t="inlineStr"/>
+      <c r="AE711" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr"/>
+      <c r="B712" t="inlineStr"/>
+      <c r="C712" t="inlineStr"/>
+      <c r="D712" t="inlineStr"/>
+      <c r="E712" t="inlineStr"/>
+      <c r="F712" t="inlineStr"/>
+      <c r="G712" t="inlineStr"/>
+      <c r="H712" t="inlineStr"/>
+      <c r="I712" t="inlineStr"/>
+      <c r="J712" t="inlineStr"/>
+      <c r="K712" t="inlineStr"/>
+      <c r="L712" t="inlineStr"/>
+      <c r="M712" t="inlineStr"/>
+      <c r="N712" t="inlineStr"/>
+      <c r="O712" t="inlineStr"/>
+      <c r="P712" t="inlineStr"/>
+      <c r="Q712" t="inlineStr"/>
+      <c r="R712" t="inlineStr"/>
+      <c r="S712" t="inlineStr"/>
+      <c r="T712" t="inlineStr"/>
+      <c r="U712" t="inlineStr"/>
+      <c r="V712" t="inlineStr"/>
+      <c r="W712" t="inlineStr"/>
+      <c r="X712" t="inlineStr"/>
+      <c r="Y712" t="inlineStr"/>
+      <c r="Z712" t="inlineStr"/>
+      <c r="AA712" t="inlineStr"/>
+      <c r="AB712" t="inlineStr"/>
+      <c r="AC712" t="inlineStr"/>
+      <c r="AD712" t="inlineStr"/>
+      <c r="AE712" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
